--- a/projects/critical_materials/excel_files/Material_intensities.xlsx
+++ b/projects/critical_materials/excel_files/Material_intensities.xlsx
@@ -66613,10 +66613,10 @@
         </is>
       </c>
       <c r="B12" s="22" t="n">
-        <v>0</v>
+        <v>0.8762886597938144</v>
       </c>
       <c r="C12" s="22" t="n">
-        <v>1</v>
+        <v>0.1237113402061856</v>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>

--- a/projects/critical_materials/excel_files/Material_intensities.xlsx
+++ b/projects/critical_materials/excel_files/Material_intensities.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10909"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10920"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Paolo/Documents/PdM_code/EnergyScope-Quebec/projects/critical_materials/excel_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57960DEF-443A-3644-9C36-63B219442ED5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D82F4D53-204B-A849-B17D-FF5B199CA5F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="36020" windowHeight="20960" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="36020" windowHeight="20960" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Table of content" sheetId="1" r:id="rId1"/>
@@ -4823,10 +4823,21 @@
     <xf numFmtId="0" fontId="13" fillId="39" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="44" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="43" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="40" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -4842,23 +4853,26 @@
     <xf numFmtId="0" fontId="16" fillId="38" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="44" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="39" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="39" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="39" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="39" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="39" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
@@ -4873,20 +4887,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="39" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="39" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="39" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="39" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -5190,26 +5190,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="183"/>
-      <c r="B1" s="184"/>
+      <c r="A1" s="176"/>
+      <c r="B1" s="177"/>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A2" s="185"/>
-      <c r="B2" s="186"/>
+      <c r="A2" s="178"/>
+      <c r="B2" s="179"/>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A3" s="187"/>
-      <c r="B3" s="188"/>
+      <c r="A3" s="180"/>
+      <c r="B3" s="181"/>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" s="19"/>
       <c r="B4" s="51"/>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A5" s="180" t="s">
+      <c r="A5" s="187" t="s">
         <v>69</v>
       </c>
-      <c r="B5" s="177"/>
+      <c r="B5" s="183"/>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" s="20" t="s">
@@ -5220,10 +5220,10 @@
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A7" s="179" t="s">
+      <c r="A7" s="186" t="s">
         <v>72</v>
       </c>
-      <c r="B7" s="177"/>
+      <c r="B7" s="183"/>
     </row>
     <row r="8" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="154" t="s">
@@ -5234,10 +5234,10 @@
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A9" s="182" t="s">
+      <c r="A9" s="189" t="s">
         <v>75</v>
       </c>
-      <c r="B9" s="177"/>
+      <c r="B9" s="183"/>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" s="155" t="s">
@@ -5280,10 +5280,10 @@
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A15" s="178" t="s">
+      <c r="A15" s="185" t="s">
         <v>86</v>
       </c>
-      <c r="B15" s="177"/>
+      <c r="B15" s="183"/>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A16" s="158" t="s">
@@ -5302,10 +5302,10 @@
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A18" s="181" t="s">
+      <c r="A18" s="188" t="s">
         <v>91</v>
       </c>
-      <c r="B18" s="177"/>
+      <c r="B18" s="183"/>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" s="160" t="s">
@@ -5316,10 +5316,10 @@
       </c>
     </row>
     <row r="20" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="176" t="s">
+      <c r="A20" s="184" t="s">
         <v>94</v>
       </c>
-      <c r="B20" s="177"/>
+      <c r="B20" s="183"/>
     </row>
     <row r="21" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="150" t="s">
@@ -5330,10 +5330,10 @@
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A22" s="189" t="s">
+      <c r="A22" s="182" t="s">
         <v>97</v>
       </c>
-      <c r="B22" s="177"/>
+      <c r="B22" s="183"/>
     </row>
     <row r="23" spans="1:2" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="161" t="s">
@@ -5360,13 +5360,13 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
-  <sheetPr codeName="Feuil10">
+  <sheetPr codeName="Feuil10" filterMode="1">
     <tabColor rgb="FFF36962"/>
   </sheetPr>
   <dimension ref="A1:E711"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="27" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="30.6640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
     <col min="3" max="3" width="32" customWidth="1"/>
     <col min="4" max="4" width="85.33203125" customWidth="1"/>
@@ -5926,7 +5926,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A36" s="105" t="s">
         <v>280</v>
       </c>
@@ -5940,7 +5940,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A37" s="105" t="s">
         <v>282</v>
       </c>
@@ -5954,7 +5954,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A38" s="105" t="s">
         <v>283</v>
       </c>
@@ -5968,7 +5968,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A39" s="105" t="s">
         <v>284</v>
       </c>
@@ -5982,7 +5982,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A40" s="105" t="s">
         <v>285</v>
       </c>
@@ -5996,7 +5996,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A41" s="105" t="s">
         <v>286</v>
       </c>
@@ -6010,7 +6010,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A42" s="105" t="s">
         <v>287</v>
       </c>
@@ -6024,7 +6024,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A43" s="105" t="s">
         <v>288</v>
       </c>
@@ -6038,7 +6038,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A44" s="105" t="s">
         <v>289</v>
       </c>
@@ -6052,7 +6052,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A45" s="105" t="s">
         <v>290</v>
       </c>
@@ -6066,7 +6066,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A46" s="105" t="s">
         <v>291</v>
       </c>
@@ -6080,7 +6080,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A47" s="105" t="s">
         <v>292</v>
       </c>
@@ -6094,7 +6094,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A48" s="105" t="s">
         <v>293</v>
       </c>
@@ -6108,7 +6108,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A49" s="105" t="s">
         <v>294</v>
       </c>
@@ -6122,7 +6122,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A50" s="105" t="s">
         <v>295</v>
       </c>
@@ -6136,7 +6136,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A51" s="105" t="s">
         <v>296</v>
       </c>
@@ -6150,7 +6150,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A52" s="105" t="s">
         <v>297</v>
       </c>
@@ -6164,7 +6164,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A53" s="105" t="s">
         <v>298</v>
       </c>
@@ -6178,7 +6178,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A54" s="105" t="s">
         <v>299</v>
       </c>
@@ -6192,7 +6192,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A55" s="105" t="s">
         <v>300</v>
       </c>
@@ -6206,7 +6206,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A56" s="105" t="s">
         <v>301</v>
       </c>
@@ -6220,7 +6220,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A57" s="105" t="s">
         <v>302</v>
       </c>
@@ -6234,7 +6234,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A58" s="105" t="s">
         <v>303</v>
       </c>
@@ -6248,7 +6248,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A59" s="105" t="s">
         <v>304</v>
       </c>
@@ -6262,7 +6262,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A60" s="105" t="s">
         <v>305</v>
       </c>
@@ -6276,7 +6276,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A61" s="105" t="s">
         <v>306</v>
       </c>
@@ -6290,7 +6290,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A62" s="105" t="s">
         <v>307</v>
       </c>
@@ -6304,7 +6304,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A63" s="105" t="s">
         <v>308</v>
       </c>
@@ -6318,7 +6318,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A64" s="105" t="s">
         <v>309</v>
       </c>
@@ -6332,7 +6332,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A65" s="105" t="s">
         <v>310</v>
       </c>
@@ -6346,7 +6346,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A66" s="105" t="s">
         <v>311</v>
       </c>
@@ -6360,7 +6360,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A67" s="105" t="s">
         <v>312</v>
       </c>
@@ -6374,7 +6374,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A68" s="105" t="s">
         <v>313</v>
       </c>
@@ -6388,7 +6388,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A69" s="105" t="s">
         <v>314</v>
       </c>
@@ -6402,7 +6402,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A70" s="105" t="s">
         <v>315</v>
       </c>
@@ -6416,7 +6416,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A71" s="105" t="s">
         <v>316</v>
       </c>
@@ -6430,7 +6430,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A72" s="105" t="s">
         <v>317</v>
       </c>
@@ -6444,7 +6444,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A73" s="105" t="s">
         <v>318</v>
       </c>
@@ -6458,7 +6458,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A74" s="105" t="s">
         <v>319</v>
       </c>
@@ -6472,7 +6472,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A75" s="105" t="s">
         <v>320</v>
       </c>
@@ -6486,7 +6486,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A76" s="105" t="s">
         <v>321</v>
       </c>
@@ -6500,7 +6500,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A77" s="105" t="s">
         <v>322</v>
       </c>
@@ -6514,7 +6514,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A78" s="105" t="s">
         <v>323</v>
       </c>
@@ -6528,7 +6528,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A79" s="105" t="s">
         <v>324</v>
       </c>
@@ -6542,7 +6542,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A80" s="105" t="s">
         <v>325</v>
       </c>
@@ -6556,7 +6556,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A81" s="105" t="s">
         <v>326</v>
       </c>
@@ -6570,7 +6570,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A82" s="105" t="s">
         <v>327</v>
       </c>
@@ -6584,7 +6584,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A83" s="105" t="s">
         <v>328</v>
       </c>
@@ -6598,7 +6598,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A84" s="105" t="s">
         <v>329</v>
       </c>
@@ -6612,7 +6612,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A85" s="105" t="s">
         <v>330</v>
       </c>
@@ -6626,7 +6626,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A86" s="105" t="s">
         <v>331</v>
       </c>
@@ -6640,7 +6640,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A87" s="105" t="s">
         <v>332</v>
       </c>
@@ -6654,7 +6654,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A88" s="105" t="s">
         <v>333</v>
       </c>
@@ -6668,7 +6668,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A89" s="105" t="s">
         <v>334</v>
       </c>
@@ -6682,7 +6682,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A90" s="105" t="s">
         <v>335</v>
       </c>
@@ -6696,7 +6696,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A91" s="105" t="s">
         <v>336</v>
       </c>
@@ -6710,7 +6710,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A92" s="105" t="s">
         <v>337</v>
       </c>
@@ -6724,7 +6724,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A93" s="105" t="s">
         <v>338</v>
       </c>
@@ -6738,7 +6738,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A94" s="105" t="s">
         <v>339</v>
       </c>
@@ -6752,7 +6752,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A95" s="105" t="s">
         <v>340</v>
       </c>
@@ -6766,7 +6766,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A96" s="105" t="s">
         <v>341</v>
       </c>
@@ -6780,7 +6780,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A97" s="105" t="s">
         <v>342</v>
       </c>
@@ -6794,7 +6794,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A98" s="105" t="s">
         <v>343</v>
       </c>
@@ -6808,7 +6808,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A99" s="105" t="s">
         <v>344</v>
       </c>
@@ -6822,7 +6822,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A100" s="105" t="s">
         <v>345</v>
       </c>
@@ -6836,7 +6836,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A101" s="105" t="s">
         <v>346</v>
       </c>
@@ -6850,7 +6850,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A102" s="105" t="s">
         <v>347</v>
       </c>
@@ -6864,7 +6864,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A103" s="105" t="s">
         <v>348</v>
       </c>
@@ -6878,7 +6878,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A104" s="105" t="s">
         <v>349</v>
       </c>
@@ -6892,7 +6892,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A105" s="105" t="s">
         <v>350</v>
       </c>
@@ -6906,7 +6906,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A106" s="105" t="s">
         <v>351</v>
       </c>
@@ -6920,7 +6920,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A107" s="105" t="s">
         <v>352</v>
       </c>
@@ -6934,7 +6934,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A108" s="105" t="s">
         <v>353</v>
       </c>
@@ -6948,7 +6948,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A109" s="105" t="s">
         <v>354</v>
       </c>
@@ -6962,7 +6962,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A110" s="105" t="s">
         <v>355</v>
       </c>
@@ -6976,7 +6976,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A111" s="105" t="s">
         <v>356</v>
       </c>
@@ -6990,7 +6990,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A112" s="105" t="s">
         <v>357</v>
       </c>
@@ -7004,7 +7004,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A113" s="105" t="s">
         <v>358</v>
       </c>
@@ -7018,7 +7018,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A114" s="105" t="s">
         <v>359</v>
       </c>
@@ -7032,7 +7032,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A115" s="105" t="s">
         <v>360</v>
       </c>
@@ -7046,7 +7046,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A116" s="105" t="s">
         <v>361</v>
       </c>
@@ -7060,7 +7060,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A117" s="105" t="s">
         <v>362</v>
       </c>
@@ -7074,7 +7074,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A118" s="105" t="s">
         <v>363</v>
       </c>
@@ -7088,7 +7088,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A119" s="105" t="s">
         <v>364</v>
       </c>
@@ -7102,7 +7102,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A120" s="105" t="s">
         <v>365</v>
       </c>
@@ -7116,7 +7116,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A121" s="105" t="s">
         <v>366</v>
       </c>
@@ -7130,7 +7130,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A122" s="105" t="s">
         <v>367</v>
       </c>
@@ -7144,7 +7144,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A123" s="105" t="s">
         <v>368</v>
       </c>
@@ -7158,7 +7158,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A124" s="105" t="s">
         <v>369</v>
       </c>
@@ -7172,7 +7172,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A125" s="105" t="s">
         <v>370</v>
       </c>
@@ -7186,7 +7186,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A126" s="105" t="s">
         <v>371</v>
       </c>
@@ -7200,7 +7200,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A127" s="105" t="s">
         <v>372</v>
       </c>
@@ -7214,7 +7214,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A128" s="105" t="s">
         <v>373</v>
       </c>
@@ -7228,7 +7228,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A129" s="105" t="s">
         <v>374</v>
       </c>
@@ -7242,7 +7242,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A130" s="105" t="s">
         <v>375</v>
       </c>
@@ -7256,7 +7256,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A131" s="105" t="s">
         <v>376</v>
       </c>
@@ -7270,7 +7270,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A132" s="105" t="s">
         <v>377</v>
       </c>
@@ -7284,7 +7284,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A133" s="105" t="s">
         <v>378</v>
       </c>
@@ -7298,7 +7298,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A134" s="105" t="s">
         <v>379</v>
       </c>
@@ -7312,7 +7312,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A135" s="105" t="s">
         <v>380</v>
       </c>
@@ -7326,7 +7326,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A136" s="105" t="s">
         <v>381</v>
       </c>
@@ -7340,7 +7340,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="137" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A137" s="105" t="s">
         <v>382</v>
       </c>
@@ -7354,7 +7354,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="138" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A138" s="105" t="s">
         <v>383</v>
       </c>
@@ -7368,7 +7368,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="139" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A139" s="105" t="s">
         <v>384</v>
       </c>
@@ -7382,7 +7382,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="140" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A140" s="105" t="s">
         <v>385</v>
       </c>
@@ -7396,7 +7396,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="141" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A141" s="105" t="s">
         <v>386</v>
       </c>
@@ -7410,7 +7410,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="142" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A142" s="105" t="s">
         <v>387</v>
       </c>
@@ -7424,7 +7424,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="143" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A143" s="105" t="s">
         <v>388</v>
       </c>
@@ -7438,7 +7438,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="144" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A144" s="105" t="s">
         <v>389</v>
       </c>
@@ -7452,7 +7452,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="145" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A145" s="105" t="s">
         <v>390</v>
       </c>
@@ -7466,7 +7466,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="146" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A146" s="105" t="s">
         <v>391</v>
       </c>
@@ -7480,7 +7480,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="147" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A147" s="105" t="s">
         <v>392</v>
       </c>
@@ -7494,7 +7494,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="148" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A148" s="105" t="s">
         <v>393</v>
       </c>
@@ -7508,7 +7508,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="149" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A149" s="105" t="s">
         <v>394</v>
       </c>
@@ -7522,7 +7522,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="150" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A150" s="105" t="s">
         <v>395</v>
       </c>
@@ -7536,7 +7536,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="151" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A151" s="105" t="s">
         <v>396</v>
       </c>
@@ -7550,7 +7550,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="152" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A152" s="105" t="s">
         <v>397</v>
       </c>
@@ -7564,7 +7564,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="153" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A153" s="105" t="s">
         <v>398</v>
       </c>
@@ -7578,7 +7578,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="154" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A154" s="105" t="s">
         <v>399</v>
       </c>
@@ -7592,7 +7592,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="155" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A155" s="105" t="s">
         <v>400</v>
       </c>
@@ -7606,7 +7606,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="156" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A156" s="105" t="s">
         <v>401</v>
       </c>
@@ -7620,7 +7620,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="157" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A157" s="105" t="s">
         <v>402</v>
       </c>
@@ -7634,7 +7634,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="158" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A158" s="105" t="s">
         <v>403</v>
       </c>
@@ -7648,7 +7648,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="159" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A159" s="105" t="s">
         <v>404</v>
       </c>
@@ -7662,7 +7662,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="160" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A160" s="105" t="s">
         <v>405</v>
       </c>
@@ -7676,7 +7676,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="161" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A161" s="105" t="s">
         <v>406</v>
       </c>
@@ -7690,7 +7690,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="162" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A162" s="105" t="s">
         <v>407</v>
       </c>
@@ -7704,7 +7704,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="163" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A163" s="105" t="s">
         <v>408</v>
       </c>
@@ -7718,7 +7718,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="164" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A164" s="105" t="s">
         <v>409</v>
       </c>
@@ -7732,7 +7732,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="165" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A165" s="105" t="s">
         <v>410</v>
       </c>
@@ -7746,7 +7746,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="166" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A166" s="105" t="s">
         <v>411</v>
       </c>
@@ -7760,7 +7760,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="167" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A167" s="105" t="s">
         <v>412</v>
       </c>
@@ -7774,7 +7774,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="168" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A168" s="105" t="s">
         <v>413</v>
       </c>
@@ -7788,7 +7788,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="169" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A169" s="105" t="s">
         <v>414</v>
       </c>
@@ -7802,7 +7802,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="170" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A170" s="105" t="s">
         <v>415</v>
       </c>
@@ -7816,7 +7816,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="171" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A171" s="105" t="s">
         <v>416</v>
       </c>
@@ -7830,7 +7830,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="172" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A172" s="105" t="s">
         <v>417</v>
       </c>
@@ -7844,7 +7844,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="173" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A173" s="105" t="s">
         <v>418</v>
       </c>
@@ -7858,7 +7858,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="174" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A174" s="105" t="s">
         <v>419</v>
       </c>
@@ -7872,7 +7872,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="175" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A175" s="105" t="s">
         <v>420</v>
       </c>
@@ -7886,7 +7886,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="176" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A176" s="105" t="s">
         <v>421</v>
       </c>
@@ -7900,7 +7900,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="177" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A177" s="105" t="s">
         <v>422</v>
       </c>
@@ -7914,7 +7914,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="178" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A178" s="105" t="s">
         <v>423</v>
       </c>
@@ -7928,7 +7928,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="179" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A179" s="105" t="s">
         <v>424</v>
       </c>
@@ -7942,7 +7942,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="180" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A180" s="105" t="s">
         <v>425</v>
       </c>
@@ -7956,7 +7956,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="181" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A181" s="105" t="s">
         <v>426</v>
       </c>
@@ -7970,7 +7970,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="182" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A182" s="105" t="s">
         <v>427</v>
       </c>
@@ -7984,7 +7984,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="183" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A183" s="105" t="s">
         <v>428</v>
       </c>
@@ -7998,7 +7998,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="184" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A184" s="105" t="s">
         <v>429</v>
       </c>
@@ -8012,7 +8012,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="185" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A185" s="105" t="s">
         <v>430</v>
       </c>
@@ -8026,7 +8026,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="186" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A186" s="105" t="s">
         <v>431</v>
       </c>
@@ -8040,7 +8040,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="187" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A187" s="105" t="s">
         <v>432</v>
       </c>
@@ -8054,7 +8054,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="188" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A188" s="105" t="s">
         <v>433</v>
       </c>
@@ -8068,7 +8068,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="189" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A189" s="105" t="s">
         <v>434</v>
       </c>
@@ -8082,7 +8082,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="190" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A190" s="105" t="s">
         <v>435</v>
       </c>
@@ -8096,7 +8096,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="191" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A191" s="105" t="s">
         <v>436</v>
       </c>
@@ -8110,7 +8110,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="192" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A192" s="105" t="s">
         <v>437</v>
       </c>
@@ -8124,7 +8124,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="193" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A193" s="105" t="s">
         <v>438</v>
       </c>
@@ -8138,7 +8138,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="194" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A194" s="105" t="s">
         <v>439</v>
       </c>
@@ -8152,7 +8152,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="195" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A195" s="105" t="s">
         <v>440</v>
       </c>
@@ -8166,7 +8166,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="196" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A196" s="106" t="s">
         <v>441</v>
       </c>
@@ -8183,7 +8183,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="197" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A197" s="107" t="s">
         <v>443</v>
       </c>
@@ -8198,7 +8198,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="198" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A198" s="108" t="s">
         <v>445</v>
       </c>
@@ -8211,7 +8211,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="199" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A199" s="108" t="s">
         <v>447</v>
       </c>
@@ -8224,7 +8224,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="200" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A200" s="107" t="s">
         <v>448</v>
       </c>
@@ -8237,7 +8237,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="201" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A201" s="107" t="s">
         <v>449</v>
       </c>
@@ -8250,7 +8250,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="202" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A202" s="107" t="s">
         <v>450</v>
       </c>
@@ -8263,7 +8263,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="203" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A203" s="107" t="s">
         <v>451</v>
       </c>
@@ -8276,7 +8276,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="204" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A204" s="109" t="s">
         <v>452</v>
       </c>
@@ -8289,7 +8289,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="205" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A205" s="107" t="s">
         <v>453</v>
       </c>
@@ -8302,7 +8302,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="206" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A206" s="107" t="s">
         <v>454</v>
       </c>
@@ -8315,7 +8315,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="207" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A207" s="107" t="s">
         <v>455</v>
       </c>
@@ -8328,7 +8328,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="208" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A208" s="107" t="s">
         <v>456</v>
       </c>
@@ -8341,7 +8341,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="209" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A209" s="107" t="s">
         <v>457</v>
       </c>
@@ -8354,7 +8354,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="210" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A210" s="107" t="s">
         <v>458</v>
       </c>
@@ -8367,7 +8367,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="211" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A211" s="107" t="s">
         <v>459</v>
       </c>
@@ -8380,7 +8380,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="212" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A212" s="107" t="s">
         <v>460</v>
       </c>
@@ -8393,7 +8393,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="213" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A213" s="107" t="s">
         <v>461</v>
       </c>
@@ -8406,7 +8406,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="214" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A214" s="107" t="s">
         <v>462</v>
       </c>
@@ -8419,7 +8419,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="215" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A215" s="107" t="s">
         <v>463</v>
       </c>
@@ -8432,7 +8432,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="216" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A216" s="107" t="s">
         <v>464</v>
       </c>
@@ -8445,7 +8445,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="217" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A217" s="107" t="s">
         <v>465</v>
       </c>
@@ -8458,7 +8458,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="218" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A218" s="107" t="s">
         <v>466</v>
       </c>
@@ -8471,7 +8471,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="219" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A219" s="107" t="s">
         <v>467</v>
       </c>
@@ -8484,7 +8484,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="220" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A220" s="110" t="s">
         <v>468</v>
       </c>
@@ -8497,7 +8497,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="221" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A221" s="110" t="s">
         <v>470</v>
       </c>
@@ -8510,7 +8510,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="222" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A222" s="110" t="s">
         <v>471</v>
       </c>
@@ -8523,7 +8523,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="223" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A223" s="110" t="s">
         <v>472</v>
       </c>
@@ -8536,7 +8536,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="224" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A224" s="110" t="s">
         <v>473</v>
       </c>
@@ -8549,7 +8549,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="225" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A225" s="110" t="s">
         <v>474</v>
       </c>
@@ -8562,7 +8562,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="226" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A226" s="110" t="s">
         <v>475</v>
       </c>
@@ -8575,7 +8575,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="227" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A227" s="110" t="s">
         <v>476</v>
       </c>
@@ -8588,7 +8588,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="228" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A228" s="111" t="s">
         <v>477</v>
       </c>
@@ -8603,7 +8603,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="229" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A229" s="111" t="s">
         <v>480</v>
       </c>
@@ -8618,7 +8618,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="230" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A230" s="111" t="s">
         <v>481</v>
       </c>
@@ -8633,7 +8633,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="231" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A231" s="111" t="s">
         <v>482</v>
       </c>
@@ -8648,7 +8648,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="232" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A232" s="111" t="s">
         <v>483</v>
       </c>
@@ -8663,7 +8663,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="233" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A233" s="111" t="s">
         <v>484</v>
       </c>
@@ -8678,7 +8678,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="234" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A234" s="111" t="s">
         <v>485</v>
       </c>
@@ -8693,7 +8693,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="235" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A235" s="111" t="s">
         <v>486</v>
       </c>
@@ -8708,7 +8708,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="236" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A236" s="111" t="s">
         <v>487</v>
       </c>
@@ -8723,7 +8723,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="237" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A237" s="111" t="s">
         <v>488</v>
       </c>
@@ -8738,7 +8738,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="238" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A238" s="111" t="s">
         <v>489</v>
       </c>
@@ -8753,7 +8753,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="239" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A239" s="111" t="s">
         <v>491</v>
       </c>
@@ -8768,7 +8768,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="240" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A240" s="111" t="s">
         <v>492</v>
       </c>
@@ -8781,7 +8781,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="241" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A241" s="111" t="s">
         <v>493</v>
       </c>
@@ -8794,7 +8794,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="242" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A242" s="111" t="s">
         <v>494</v>
       </c>
@@ -8809,7 +8809,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="243" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A243" s="111" t="s">
         <v>495</v>
       </c>
@@ -8824,7 +8824,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="244" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A244" s="111" t="s">
         <v>496</v>
       </c>
@@ -8839,7 +8839,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="245" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A245" s="111" t="s">
         <v>498</v>
       </c>
@@ -8854,7 +8854,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="246" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A246" s="111" t="s">
         <v>499</v>
       </c>
@@ -8869,7 +8869,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="247" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A247" s="111" t="s">
         <v>500</v>
       </c>
@@ -8884,7 +8884,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="248" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A248" s="112" t="s">
         <v>501</v>
       </c>
@@ -8897,7 +8897,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="249" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A249" s="112" t="s">
         <v>503</v>
       </c>
@@ -8910,7 +8910,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="250" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="250" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A250" s="112" t="s">
         <v>504</v>
       </c>
@@ -8923,7 +8923,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="251" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A251" s="112" t="s">
         <v>505</v>
       </c>
@@ -8936,7 +8936,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="252" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A252" s="112" t="s">
         <v>506</v>
       </c>
@@ -8949,7 +8949,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="253" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="253" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A253" s="112" t="s">
         <v>507</v>
       </c>
@@ -8962,7 +8962,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="254" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="254" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A254" s="108" t="s">
         <v>508</v>
       </c>
@@ -8975,7 +8975,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="255" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="255" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A255" s="112" t="s">
         <v>509</v>
       </c>
@@ -8988,7 +8988,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="256" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="256" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A256" s="112" t="s">
         <v>510</v>
       </c>
@@ -9001,7 +9001,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="257" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="257" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A257" s="112" t="s">
         <v>511</v>
       </c>
@@ -9014,7 +9014,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="258" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="258" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A258" s="112" t="s">
         <v>512</v>
       </c>
@@ -9027,7 +9027,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="259" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="259" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A259" s="112" t="s">
         <v>513</v>
       </c>
@@ -9040,7 +9040,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="260" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="260" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A260" s="112" t="s">
         <v>514</v>
       </c>
@@ -9053,7 +9053,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="261" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="261" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A261" s="111" t="s">
         <v>515</v>
       </c>
@@ -9068,7 +9068,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="262" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="262" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A262" s="111" t="s">
         <v>516</v>
       </c>
@@ -9083,7 +9083,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="263" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="263" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A263" s="111" t="s">
         <v>517</v>
       </c>
@@ -9098,7 +9098,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="264" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="264" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A264" s="111" t="s">
         <v>518</v>
       </c>
@@ -9113,7 +9113,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="265" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="265" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A265" s="111" t="s">
         <v>519</v>
       </c>
@@ -9128,7 +9128,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="266" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="266" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A266" s="111" t="s">
         <v>520</v>
       </c>
@@ -9143,7 +9143,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="267" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="267" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A267" s="111" t="s">
         <v>521</v>
       </c>
@@ -9158,7 +9158,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="268" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="268" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A268" s="111" t="s">
         <v>522</v>
       </c>
@@ -9173,7 +9173,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="269" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="269" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A269" s="111" t="s">
         <v>523</v>
       </c>
@@ -9188,7 +9188,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="270" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="270" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A270" s="111" t="s">
         <v>524</v>
       </c>
@@ -9203,7 +9203,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="271" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="271" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A271" s="111" t="s">
         <v>525</v>
       </c>
@@ -9218,7 +9218,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="272" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="272" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A272" s="111" t="s">
         <v>526</v>
       </c>
@@ -9233,7 +9233,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="273" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="273" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A273" s="111" t="s">
         <v>527</v>
       </c>
@@ -9248,7 +9248,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="274" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="274" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A274" s="111" t="s">
         <v>528</v>
       </c>
@@ -9263,7 +9263,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="275" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="275" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A275" s="111" t="s">
         <v>529</v>
       </c>
@@ -9278,7 +9278,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="276" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="276" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A276" s="111" t="s">
         <v>530</v>
       </c>
@@ -9293,7 +9293,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="277" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="277" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A277" s="111" t="s">
         <v>531</v>
       </c>
@@ -9308,7 +9308,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="278" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="278" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A278" s="111" t="s">
         <v>532</v>
       </c>
@@ -9323,7 +9323,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="279" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="279" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A279" s="111" t="s">
         <v>533</v>
       </c>
@@ -9338,7 +9338,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="280" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="280" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A280" s="111" t="s">
         <v>534</v>
       </c>
@@ -9353,7 +9353,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="281" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="281" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A281" s="111" t="s">
         <v>535</v>
       </c>
@@ -9368,7 +9368,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="282" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="282" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A282" s="111" t="s">
         <v>536</v>
       </c>
@@ -9383,7 +9383,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="283" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="283" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A283" s="111" t="s">
         <v>537</v>
       </c>
@@ -9398,7 +9398,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="284" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="284" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A284" s="111" t="s">
         <v>538</v>
       </c>
@@ -9413,7 +9413,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="285" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="285" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A285" s="111" t="s">
         <v>539</v>
       </c>
@@ -9428,7 +9428,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="286" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="286" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A286" s="111" t="s">
         <v>540</v>
       </c>
@@ -9443,7 +9443,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="287" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="287" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A287" s="111" t="s">
         <v>541</v>
       </c>
@@ -9458,7 +9458,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="288" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="288" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A288" s="111" t="s">
         <v>542</v>
       </c>
@@ -9473,7 +9473,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="289" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="289" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A289" s="111" t="s">
         <v>543</v>
       </c>
@@ -9488,7 +9488,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="290" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="290" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A290" s="111" t="s">
         <v>544</v>
       </c>
@@ -9503,7 +9503,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="291" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="291" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A291" s="111" t="s">
         <v>545</v>
       </c>
@@ -9518,7 +9518,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="292" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="292" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A292" s="111" t="s">
         <v>546</v>
       </c>
@@ -9533,7 +9533,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="293" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="293" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A293" s="111" t="s">
         <v>547</v>
       </c>
@@ -9548,7 +9548,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="294" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="294" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A294" s="111" t="s">
         <v>548</v>
       </c>
@@ -9563,7 +9563,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="295" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="295" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A295" s="111" t="s">
         <v>549</v>
       </c>
@@ -9578,7 +9578,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="296" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="296" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A296" s="111" t="s">
         <v>550</v>
       </c>
@@ -9593,7 +9593,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="297" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="297" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A297" s="111" t="s">
         <v>551</v>
       </c>
@@ -9608,7 +9608,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="298" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="298" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A298" s="111" t="s">
         <v>552</v>
       </c>
@@ -9623,7 +9623,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="299" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="299" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A299" s="111" t="s">
         <v>553</v>
       </c>
@@ -9638,7 +9638,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="300" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="300" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A300" s="111" t="s">
         <v>554</v>
       </c>
@@ -9653,7 +9653,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="301" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="301" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A301" s="111" t="s">
         <v>555</v>
       </c>
@@ -9668,7 +9668,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="302" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="302" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A302" s="111" t="s">
         <v>556</v>
       </c>
@@ -9683,7 +9683,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="303" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="303" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A303" s="111" t="s">
         <v>557</v>
       </c>
@@ -9698,7 +9698,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="304" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="304" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A304" s="111" t="s">
         <v>558</v>
       </c>
@@ -9713,7 +9713,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="305" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="305" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A305" s="107" t="s">
         <v>559</v>
       </c>
@@ -9726,7 +9726,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="306" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="306" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A306" s="107" t="s">
         <v>560</v>
       </c>
@@ -9739,7 +9739,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="307" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="307" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A307" s="107" t="s">
         <v>561</v>
       </c>
@@ -9752,7 +9752,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="308" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="308" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A308" s="107" t="s">
         <v>562</v>
       </c>
@@ -9765,7 +9765,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="309" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="309" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A309" s="111" t="s">
         <v>563</v>
       </c>
@@ -9778,7 +9778,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="310" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="310" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A310" s="111" t="s">
         <v>564</v>
       </c>
@@ -9791,7 +9791,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="311" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="311" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A311" s="111" t="s">
         <v>565</v>
       </c>
@@ -9804,7 +9804,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="312" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="312" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A312" s="111" t="s">
         <v>566</v>
       </c>
@@ -9817,7 +9817,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="313" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="313" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A313" s="111" t="s">
         <v>567</v>
       </c>
@@ -9830,7 +9830,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="314" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="314" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A314" s="111" t="s">
         <v>568</v>
       </c>
@@ -9843,7 +9843,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="315" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="315" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A315" s="110" t="s">
         <v>569</v>
       </c>
@@ -9856,7 +9856,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="316" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="316" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A316" s="110" t="s">
         <v>570</v>
       </c>
@@ -9869,7 +9869,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="317" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="317" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A317" s="110" t="s">
         <v>571</v>
       </c>
@@ -9882,7 +9882,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="318" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="318" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A318" s="110" t="s">
         <v>572</v>
       </c>
@@ -9895,7 +9895,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="319" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="319" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A319" s="110" t="s">
         <v>573</v>
       </c>
@@ -9908,7 +9908,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="320" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="320" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A320" s="110" t="s">
         <v>574</v>
       </c>
@@ -9921,7 +9921,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="321" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="321" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A321" s="110" t="s">
         <v>575</v>
       </c>
@@ -9934,7 +9934,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="322" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="322" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A322" s="110" t="s">
         <v>576</v>
       </c>
@@ -9947,7 +9947,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="323" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="323" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A323" s="107" t="s">
         <v>577</v>
       </c>
@@ -9960,7 +9960,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="324" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="324" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A324" s="107" t="s">
         <v>578</v>
       </c>
@@ -9973,7 +9973,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="325" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="325" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A325" s="107" t="s">
         <v>579</v>
       </c>
@@ -9986,7 +9986,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="326" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="326" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A326" s="112" t="s">
         <v>580</v>
       </c>
@@ -9999,7 +9999,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="327" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="327" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A327" s="112" t="s">
         <v>581</v>
       </c>
@@ -10012,7 +10012,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="328" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="328" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A328" s="113" t="s">
         <v>582</v>
       </c>
@@ -10025,7 +10025,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="329" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="329" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A329" s="113" t="s">
         <v>584</v>
       </c>
@@ -10038,7 +10038,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="330" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="330" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A330" s="113" t="s">
         <v>585</v>
       </c>
@@ -10051,7 +10051,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="331" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="331" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A331" s="113" t="s">
         <v>586</v>
       </c>
@@ -10064,7 +10064,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="332" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="332" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A332" s="113" t="s">
         <v>587</v>
       </c>
@@ -10077,7 +10077,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="333" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="333" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A333" s="113" t="s">
         <v>588</v>
       </c>
@@ -10090,7 +10090,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="334" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="334" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A334" s="113" t="s">
         <v>589</v>
       </c>
@@ -10103,7 +10103,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="335" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="335" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A335" s="113" t="s">
         <v>590</v>
       </c>
@@ -10116,7 +10116,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="336" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="336" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A336" s="113" t="s">
         <v>591</v>
       </c>
@@ -10129,7 +10129,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="337" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="337" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A337" s="113" t="s">
         <v>592</v>
       </c>
@@ -10142,7 +10142,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="338" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="338" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A338" s="113" t="s">
         <v>593</v>
       </c>
@@ -10155,7 +10155,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="339" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="339" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A339" s="113" t="s">
         <v>594</v>
       </c>
@@ -10168,7 +10168,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="340" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="340" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A340" s="113" t="s">
         <v>595</v>
       </c>
@@ -10181,7 +10181,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="341" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="341" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A341" s="113" t="s">
         <v>596</v>
       </c>
@@ -10194,7 +10194,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="342" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="342" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A342" s="113" t="s">
         <v>597</v>
       </c>
@@ -10207,7 +10207,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="343" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="343" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A343" s="113" t="s">
         <v>598</v>
       </c>
@@ -10220,7 +10220,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="344" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="344" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A344" s="113" t="s">
         <v>599</v>
       </c>
@@ -10233,7 +10233,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="345" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="345" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A345" s="113" t="s">
         <v>600</v>
       </c>
@@ -10246,7 +10246,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="346" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="346" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A346" s="112" t="s">
         <v>601</v>
       </c>
@@ -10259,7 +10259,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="347" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="347" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A347" s="113" t="s">
         <v>602</v>
       </c>
@@ -10272,7 +10272,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="348" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="348" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A348" s="113" t="s">
         <v>603</v>
       </c>
@@ -10285,7 +10285,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="349" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="349" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A349" s="113" t="s">
         <v>604</v>
       </c>
@@ -10298,7 +10298,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="350" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="350" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A350" s="113" t="s">
         <v>605</v>
       </c>
@@ -10311,7 +10311,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="351" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="351" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A351" s="113" t="s">
         <v>606</v>
       </c>
@@ -10324,7 +10324,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="352" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="352" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A352" s="113" t="s">
         <v>607</v>
       </c>
@@ -10337,7 +10337,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="353" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="353" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A353" s="113" t="s">
         <v>608</v>
       </c>
@@ -10350,7 +10350,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="354" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="354" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A354" s="113" t="s">
         <v>609</v>
       </c>
@@ -10363,7 +10363,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="355" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="355" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A355" s="113" t="s">
         <v>610</v>
       </c>
@@ -10376,7 +10376,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="356" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="356" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A356" s="113" t="s">
         <v>611</v>
       </c>
@@ -10389,7 +10389,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="357" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="357" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A357" s="113" t="s">
         <v>612</v>
       </c>
@@ -10402,7 +10402,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="358" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="358" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A358" s="113" t="s">
         <v>613</v>
       </c>
@@ -10415,7 +10415,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="359" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="359" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A359" s="113" t="s">
         <v>614</v>
       </c>
@@ -10428,7 +10428,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="360" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="360" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A360" s="113" t="s">
         <v>615</v>
       </c>
@@ -10441,7 +10441,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="361" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="361" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A361" s="113" t="s">
         <v>616</v>
       </c>
@@ -10454,7 +10454,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="362" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="362" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A362" s="109" t="s">
         <v>617</v>
       </c>
@@ -10467,7 +10467,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="363" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="363" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A363" s="114" t="s">
         <v>618</v>
       </c>
@@ -10480,7 +10480,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="364" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="364" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A364" s="112" t="s">
         <v>620</v>
       </c>
@@ -10493,7 +10493,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="365" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="365" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A365" s="114" t="s">
         <v>621</v>
       </c>
@@ -10506,7 +10506,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="366" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="366" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A366" s="114" t="s">
         <v>622</v>
       </c>
@@ -10519,7 +10519,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="367" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="367" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A367" s="114" t="s">
         <v>623</v>
       </c>
@@ -10532,7 +10532,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="368" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="368" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A368" s="109" t="s">
         <v>624</v>
       </c>
@@ -10545,7 +10545,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="369" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="369" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A369" s="112" t="s">
         <v>625</v>
       </c>
@@ -10558,7 +10558,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="370" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="370" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A370" s="107" t="s">
         <v>626</v>
       </c>
@@ -10571,7 +10571,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="371" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="371" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A371" s="107" t="s">
         <v>627</v>
       </c>
@@ -10584,7 +10584,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="372" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="372" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A372" s="107" t="s">
         <v>628</v>
       </c>
@@ -10597,7 +10597,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="373" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="373" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A373" s="107" t="s">
         <v>629</v>
       </c>
@@ -10610,7 +10610,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="374" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="374" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A374" s="108" t="s">
         <v>630</v>
       </c>
@@ -10623,7 +10623,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="375" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="375" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A375" s="108" t="s">
         <v>631</v>
       </c>
@@ -10636,7 +10636,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="376" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="376" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A376" s="108" t="s">
         <v>632</v>
       </c>
@@ -10649,7 +10649,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="377" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="377" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A377" s="108" t="s">
         <v>633</v>
       </c>
@@ -10662,7 +10662,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="378" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="378" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A378" s="107" t="s">
         <v>634</v>
       </c>
@@ -10675,7 +10675,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="379" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="379" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A379" s="107" t="s">
         <v>635</v>
       </c>
@@ -10688,7 +10688,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="380" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="380" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A380" s="107" t="s">
         <v>636</v>
       </c>
@@ -10701,7 +10701,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="381" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="381" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A381" s="109" t="s">
         <v>637</v>
       </c>
@@ -10714,7 +10714,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="382" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="382" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A382" s="107" t="s">
         <v>638</v>
       </c>
@@ -10727,7 +10727,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="383" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="383" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A383" s="107" t="s">
         <v>639</v>
       </c>
@@ -10740,7 +10740,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="384" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="384" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A384" s="107" t="s">
         <v>640</v>
       </c>
@@ -10753,7 +10753,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="385" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="385" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A385" s="107" t="s">
         <v>641</v>
       </c>
@@ -10766,7 +10766,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="386" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="386" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A386" s="107" t="s">
         <v>642</v>
       </c>
@@ -10779,7 +10779,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="387" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="387" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A387" s="107" t="s">
         <v>643</v>
       </c>
@@ -10792,7 +10792,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="388" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="388" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A388" s="107" t="s">
         <v>644</v>
       </c>
@@ -10805,7 +10805,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="389" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="389" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A389" s="107" t="s">
         <v>645</v>
       </c>
@@ -10818,7 +10818,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="390" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="390" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A390" s="107" t="s">
         <v>646</v>
       </c>
@@ -10831,7 +10831,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="391" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="391" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A391" s="109" t="s">
         <v>647</v>
       </c>
@@ -10844,7 +10844,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="392" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="392" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A392" s="114" t="s">
         <v>648</v>
       </c>
@@ -10857,7 +10857,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="393" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="393" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A393" s="114" t="s">
         <v>649</v>
       </c>
@@ -10870,7 +10870,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="394" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="394" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A394" s="114" t="s">
         <v>650</v>
       </c>
@@ -10883,7 +10883,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="395" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="395" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A395" s="114" t="s">
         <v>651</v>
       </c>
@@ -10896,7 +10896,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="396" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="396" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A396" s="114" t="s">
         <v>652</v>
       </c>
@@ -10922,7 +10922,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="398" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="398" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A398" s="115" t="s">
         <v>654</v>
       </c>
@@ -10935,7 +10935,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="399" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="399" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A399" s="115" t="s">
         <v>656</v>
       </c>
@@ -10948,7 +10948,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="400" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="400" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A400" s="115" t="s">
         <v>657</v>
       </c>
@@ -10961,7 +10961,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="401" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="401" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A401" s="115" t="s">
         <v>658</v>
       </c>
@@ -10974,7 +10974,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="402" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="402" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A402" s="115" t="s">
         <v>659</v>
       </c>
@@ -10987,7 +10987,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="403" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="403" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A403" s="115" t="s">
         <v>660</v>
       </c>
@@ -11000,7 +11000,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="404" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="404" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A404" s="115" t="s">
         <v>661</v>
       </c>
@@ -11013,7 +11013,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="405" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="405" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A405" s="115" t="s">
         <v>662</v>
       </c>
@@ -11026,7 +11026,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="406" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="406" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A406" s="115" t="s">
         <v>663</v>
       </c>
@@ -11039,7 +11039,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="407" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="407" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A407" s="115" t="s">
         <v>664</v>
       </c>
@@ -11052,7 +11052,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="408" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="408" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A408" s="115" t="s">
         <v>665</v>
       </c>
@@ -11065,7 +11065,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="409" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="409" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A409" s="115" t="s">
         <v>666</v>
       </c>
@@ -11078,7 +11078,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="410" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="410" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A410" s="115" t="s">
         <v>667</v>
       </c>
@@ -11091,7 +11091,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="411" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="411" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A411" s="115" t="s">
         <v>668</v>
       </c>
@@ -11104,7 +11104,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="412" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="412" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A412" s="115" t="s">
         <v>669</v>
       </c>
@@ -11117,7 +11117,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="413" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="413" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A413" s="110" t="s">
         <v>670</v>
       </c>
@@ -11130,7 +11130,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="414" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="414" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A414" s="110" t="s">
         <v>671</v>
       </c>
@@ -11143,7 +11143,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="415" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="415" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A415" s="110" t="s">
         <v>672</v>
       </c>
@@ -11156,7 +11156,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="416" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="416" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A416" s="110" t="s">
         <v>673</v>
       </c>
@@ -11169,7 +11169,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="417" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="417" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A417" s="110" t="s">
         <v>674</v>
       </c>
@@ -11182,7 +11182,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="418" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="418" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A418" s="110" t="s">
         <v>675</v>
       </c>
@@ -11195,7 +11195,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="419" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="419" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A419" s="110" t="s">
         <v>676</v>
       </c>
@@ -11208,7 +11208,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="420" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="420" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A420" s="110" t="s">
         <v>677</v>
       </c>
@@ -11221,7 +11221,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="421" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="421" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A421" s="110" t="s">
         <v>678</v>
       </c>
@@ -11234,7 +11234,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="422" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="422" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A422" s="110" t="s">
         <v>679</v>
       </c>
@@ -11247,7 +11247,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="423" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="423" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A423" s="110" t="s">
         <v>680</v>
       </c>
@@ -11260,7 +11260,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="424" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="424" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A424" s="110" t="s">
         <v>681</v>
       </c>
@@ -11273,7 +11273,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="425" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="425" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A425" s="110" t="s">
         <v>682</v>
       </c>
@@ -11286,7 +11286,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="426" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="426" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A426" s="110" t="s">
         <v>683</v>
       </c>
@@ -11299,7 +11299,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="427" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="427" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A427" s="110" t="s">
         <v>684</v>
       </c>
@@ -11312,7 +11312,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="428" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="428" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A428" s="110" t="s">
         <v>685</v>
       </c>
@@ -11325,7 +11325,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="429" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="429" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A429" s="110" t="s">
         <v>686</v>
       </c>
@@ -11338,7 +11338,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="430" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="430" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A430" s="110" t="s">
         <v>687</v>
       </c>
@@ -11351,7 +11351,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="431" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="431" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A431" s="110" t="s">
         <v>688</v>
       </c>
@@ -11364,7 +11364,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="432" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="432" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A432" s="110" t="s">
         <v>689</v>
       </c>
@@ -11377,7 +11377,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="433" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="433" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A433" s="110" t="s">
         <v>690</v>
       </c>
@@ -11390,7 +11390,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="434" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="434" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A434" s="110" t="s">
         <v>691</v>
       </c>
@@ -11403,7 +11403,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="435" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="435" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A435" s="110" t="s">
         <v>692</v>
       </c>
@@ -11416,7 +11416,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="436" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="436" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A436" s="110" t="s">
         <v>693</v>
       </c>
@@ -11429,7 +11429,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="437" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="437" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A437" s="110" t="s">
         <v>694</v>
       </c>
@@ -11442,7 +11442,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="438" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="438" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A438" s="110" t="s">
         <v>695</v>
       </c>
@@ -11455,7 +11455,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="439" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="439" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A439" s="110" t="s">
         <v>696</v>
       </c>
@@ -11468,7 +11468,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="440" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="440" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A440" s="110" t="s">
         <v>697</v>
       </c>
@@ -11481,7 +11481,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="441" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="441" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A441" s="110" t="s">
         <v>698</v>
       </c>
@@ -11494,7 +11494,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="442" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="442" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A442" s="110" t="s">
         <v>699</v>
       </c>
@@ -11507,7 +11507,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="443" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="443" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A443" s="110" t="s">
         <v>700</v>
       </c>
@@ -11520,7 +11520,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="444" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="444" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A444" s="110" t="s">
         <v>701</v>
       </c>
@@ -11533,7 +11533,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="445" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="445" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A445" s="110" t="s">
         <v>702</v>
       </c>
@@ -11546,7 +11546,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="446" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="446" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A446" s="110" t="s">
         <v>703</v>
       </c>
@@ -11559,7 +11559,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="447" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="447" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A447" s="110" t="s">
         <v>704</v>
       </c>
@@ -11572,7 +11572,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="448" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="448" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A448" s="110" t="s">
         <v>705</v>
       </c>
@@ -11585,7 +11585,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="449" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="449" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A449" s="114" t="s">
         <v>706</v>
       </c>
@@ -11598,7 +11598,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="450" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="450" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A450" s="114" t="s">
         <v>707</v>
       </c>
@@ -11611,7 +11611,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="451" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="451" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A451" s="114" t="s">
         <v>708</v>
       </c>
@@ -11624,7 +11624,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="452" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="452" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A452" s="114" t="s">
         <v>709</v>
       </c>
@@ -11637,7 +11637,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="453" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="453" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A453" s="114" t="s">
         <v>710</v>
       </c>
@@ -11650,7 +11650,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="454" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="454" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A454" s="107" t="s">
         <v>711</v>
       </c>
@@ -11663,7 +11663,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="455" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="455" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A455" s="107" t="s">
         <v>712</v>
       </c>
@@ -11676,7 +11676,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="456" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="456" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A456" s="107" t="s">
         <v>713</v>
       </c>
@@ -11689,7 +11689,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="457" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="457" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A457" s="107" t="s">
         <v>714</v>
       </c>
@@ -11702,7 +11702,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="458" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="458" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A458" s="107" t="s">
         <v>715</v>
       </c>
@@ -11715,7 +11715,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="459" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="459" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A459" s="107" t="s">
         <v>716</v>
       </c>
@@ -11728,7 +11728,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="460" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="460" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A460" s="107" t="s">
         <v>717</v>
       </c>
@@ -11741,7 +11741,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="461" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="461" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A461" s="109" t="s">
         <v>718</v>
       </c>
@@ -11754,7 +11754,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="462" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="462" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A462" s="114" t="s">
         <v>719</v>
       </c>
@@ -11767,7 +11767,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="463" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="463" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A463" s="114" t="s">
         <v>720</v>
       </c>
@@ -11780,7 +11780,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="464" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="464" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A464" s="114" t="s">
         <v>721</v>
       </c>
@@ -11793,7 +11793,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="465" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="465" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A465" s="107" t="s">
         <v>722</v>
       </c>
@@ -11806,7 +11806,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="466" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="466" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A466" s="107" t="s">
         <v>723</v>
       </c>
@@ -11819,7 +11819,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="467" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="467" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A467" s="107" t="s">
         <v>724</v>
       </c>
@@ -11832,7 +11832,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="468" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="468" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A468" s="107" t="s">
         <v>725</v>
       </c>
@@ -11845,7 +11845,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="469" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="469" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A469" s="107" t="s">
         <v>726</v>
       </c>
@@ -11858,7 +11858,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="470" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="470" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A470" s="107" t="s">
         <v>727</v>
       </c>
@@ -11871,7 +11871,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="471" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="471" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A471" s="107" t="s">
         <v>728</v>
       </c>
@@ -11884,7 +11884,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="472" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="472" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A472" s="107" t="s">
         <v>729</v>
       </c>
@@ -11897,7 +11897,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="473" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="473" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A473" s="107" t="s">
         <v>730</v>
       </c>
@@ -11910,7 +11910,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="474" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="474" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A474" s="107" t="s">
         <v>731</v>
       </c>
@@ -11923,7 +11923,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="475" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="475" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A475" s="107" t="s">
         <v>732</v>
       </c>
@@ -11936,7 +11936,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="476" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="476" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A476" s="107" t="s">
         <v>733</v>
       </c>
@@ -11949,7 +11949,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="477" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="477" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A477" s="109" t="s">
         <v>734</v>
       </c>
@@ -11962,7 +11962,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="478" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="478" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A478" s="110" t="s">
         <v>735</v>
       </c>
@@ -11975,7 +11975,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="479" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="479" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A479" s="110" t="s">
         <v>736</v>
       </c>
@@ -11988,7 +11988,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="480" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="480" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A480" s="110" t="s">
         <v>737</v>
       </c>
@@ -12001,7 +12001,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="481" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="481" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A481" s="110" t="s">
         <v>738</v>
       </c>
@@ -12014,7 +12014,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="482" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="482" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A482" s="110" t="s">
         <v>739</v>
       </c>
@@ -12027,7 +12027,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="483" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="483" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A483" s="110" t="s">
         <v>740</v>
       </c>
@@ -12040,7 +12040,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="484" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="484" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A484" s="110" t="s">
         <v>741</v>
       </c>
@@ -12053,7 +12053,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="485" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="485" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A485" s="110" t="s">
         <v>742</v>
       </c>
@@ -12066,7 +12066,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="486" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="486" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A486" s="108" t="s">
         <v>743</v>
       </c>
@@ -12079,7 +12079,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="487" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="487" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A487" s="108" t="s">
         <v>744</v>
       </c>
@@ -12092,7 +12092,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="488" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="488" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A488" s="108" t="s">
         <v>745</v>
       </c>
@@ -12105,7 +12105,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="489" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="489" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A489" s="107" t="s">
         <v>746</v>
       </c>
@@ -12120,7 +12120,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="490" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="490" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A490" s="108" t="s">
         <v>747</v>
       </c>
@@ -12133,7 +12133,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="491" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="491" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A491" s="110" t="s">
         <v>748</v>
       </c>
@@ -12146,7 +12146,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="492" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="492" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A492" s="110" t="s">
         <v>749</v>
       </c>
@@ -12159,7 +12159,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="493" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="493" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A493" s="110" t="s">
         <v>750</v>
       </c>
@@ -12172,7 +12172,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="494" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="494" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A494" s="110" t="s">
         <v>751</v>
       </c>
@@ -12185,7 +12185,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="495" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="495" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A495" s="111" t="s">
         <v>752</v>
       </c>
@@ -12198,7 +12198,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="496" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="496" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A496" s="111" t="s">
         <v>753</v>
       </c>
@@ -12211,7 +12211,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="497" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="497" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A497" s="111" t="s">
         <v>754</v>
       </c>
@@ -12224,7 +12224,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="498" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="498" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A498" s="111" t="s">
         <v>755</v>
       </c>
@@ -12237,7 +12237,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="499" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="499" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A499" s="111" t="s">
         <v>756</v>
       </c>
@@ -12250,7 +12250,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="500" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="500" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A500" s="111" t="s">
         <v>757</v>
       </c>
@@ -12263,7 +12263,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="501" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="501" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A501" s="111" t="s">
         <v>758</v>
       </c>
@@ -12276,7 +12276,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="502" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="502" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A502" s="111" t="s">
         <v>759</v>
       </c>
@@ -12289,7 +12289,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="503" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="503" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A503" s="108" t="s">
         <v>760</v>
       </c>
@@ -12302,7 +12302,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="504" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="504" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A504" s="108" t="s">
         <v>761</v>
       </c>
@@ -12315,7 +12315,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="505" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="505" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A505" s="107" t="s">
         <v>762</v>
       </c>
@@ -12328,7 +12328,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="506" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="506" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A506" s="111" t="s">
         <v>763</v>
       </c>
@@ -12343,7 +12343,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="507" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="507" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A507" s="111" t="s">
         <v>764</v>
       </c>
@@ -12358,7 +12358,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="508" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="508" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A508" s="111" t="s">
         <v>765</v>
       </c>
@@ -12373,7 +12373,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="509" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="509" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A509" s="111" t="s">
         <v>766</v>
       </c>
@@ -12388,7 +12388,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="510" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="510" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A510" s="111" t="s">
         <v>767</v>
       </c>
@@ -12403,7 +12403,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="511" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="511" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A511" s="111" t="s">
         <v>768</v>
       </c>
@@ -12418,7 +12418,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="512" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="512" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A512" s="111" t="s">
         <v>769</v>
       </c>
@@ -12433,7 +12433,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="513" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="513" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A513" s="111" t="s">
         <v>770</v>
       </c>
@@ -12448,7 +12448,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="514" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="514" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A514" s="111" t="s">
         <v>771</v>
       </c>
@@ -12463,7 +12463,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="515" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="515" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A515" s="111" t="s">
         <v>772</v>
       </c>
@@ -12478,7 +12478,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="516" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="516" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A516" s="111" t="s">
         <v>773</v>
       </c>
@@ -12493,7 +12493,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="517" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="517" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A517" s="111" t="s">
         <v>774</v>
       </c>
@@ -12508,7 +12508,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="518" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="518" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A518" s="111" t="s">
         <v>775</v>
       </c>
@@ -12523,7 +12523,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="519" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="519" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A519" s="111" t="s">
         <v>776</v>
       </c>
@@ -12538,7 +12538,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="520" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="520" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A520" s="111" t="s">
         <v>777</v>
       </c>
@@ -12553,7 +12553,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="521" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="521" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A521" s="111" t="s">
         <v>778</v>
       </c>
@@ -12568,7 +12568,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="522" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="522" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A522" s="111" t="s">
         <v>779</v>
       </c>
@@ -12583,7 +12583,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="523" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="523" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A523" s="111" t="s">
         <v>780</v>
       </c>
@@ -12598,7 +12598,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="524" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="524" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A524" s="111" t="s">
         <v>781</v>
       </c>
@@ -12613,7 +12613,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="525" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="525" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A525" s="111" t="s">
         <v>782</v>
       </c>
@@ -12628,7 +12628,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="526" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="526" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A526" s="111" t="s">
         <v>783</v>
       </c>
@@ -12643,7 +12643,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="527" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="527" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A527" s="111" t="s">
         <v>784</v>
       </c>
@@ -12658,7 +12658,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="528" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="528" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A528" s="110" t="s">
         <v>785</v>
       </c>
@@ -12671,7 +12671,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="529" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="529" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A529" s="110" t="s">
         <v>786</v>
       </c>
@@ -12684,7 +12684,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="530" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="530" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A530" s="110" t="s">
         <v>787</v>
       </c>
@@ -12697,7 +12697,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="531" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="531" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A531" s="110" t="s">
         <v>788</v>
       </c>
@@ -12710,7 +12710,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="532" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="532" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A532" s="110" t="s">
         <v>789</v>
       </c>
@@ -12723,7 +12723,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="533" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="533" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A533" s="110" t="s">
         <v>790</v>
       </c>
@@ -12736,7 +12736,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="534" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="534" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A534" s="110" t="s">
         <v>791</v>
       </c>
@@ -12749,7 +12749,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="535" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="535" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A535" s="110" t="s">
         <v>792</v>
       </c>
@@ -12762,7 +12762,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="536" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="536" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A536" s="110" t="s">
         <v>793</v>
       </c>
@@ -12775,7 +12775,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="537" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="537" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A537" s="110" t="s">
         <v>794</v>
       </c>
@@ -12788,7 +12788,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="538" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="538" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A538" s="110" t="s">
         <v>795</v>
       </c>
@@ -12801,7 +12801,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="539" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="539" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A539" s="110" t="s">
         <v>796</v>
       </c>
@@ -12814,7 +12814,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="540" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="540" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A540" s="110" t="s">
         <v>797</v>
       </c>
@@ -12827,7 +12827,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="541" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="541" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A541" s="110" t="s">
         <v>798</v>
       </c>
@@ -12840,7 +12840,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="542" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="542" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A542" s="110" t="s">
         <v>799</v>
       </c>
@@ -12853,7 +12853,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="543" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="543" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A543" s="110" t="s">
         <v>800</v>
       </c>
@@ -12866,7 +12866,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="544" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="544" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A544" s="110" t="s">
         <v>801</v>
       </c>
@@ -12879,7 +12879,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="545" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="545" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A545" s="110" t="s">
         <v>802</v>
       </c>
@@ -12892,7 +12892,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="546" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="546" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A546" s="110" t="s">
         <v>803</v>
       </c>
@@ -12905,7 +12905,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="547" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="547" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A547" s="110" t="s">
         <v>804</v>
       </c>
@@ -12918,7 +12918,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="548" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="548" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A548" s="110" t="s">
         <v>805</v>
       </c>
@@ -12931,7 +12931,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="549" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="549" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A549" s="110" t="s">
         <v>806</v>
       </c>
@@ -12944,7 +12944,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="550" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="550" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A550" s="110" t="s">
         <v>807</v>
       </c>
@@ -12957,7 +12957,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="551" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="551" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A551" s="110" t="s">
         <v>808</v>
       </c>
@@ -12970,7 +12970,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="552" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="552" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A552" s="110" t="s">
         <v>809</v>
       </c>
@@ -12983,7 +12983,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="553" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="553" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A553" s="110" t="s">
         <v>810</v>
       </c>
@@ -12996,7 +12996,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="554" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="554" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A554" s="110" t="s">
         <v>811</v>
       </c>
@@ -13009,7 +13009,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="555" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="555" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A555" s="110" t="s">
         <v>812</v>
       </c>
@@ -13022,7 +13022,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="556" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="556" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A556" s="110" t="s">
         <v>813</v>
       </c>
@@ -13035,7 +13035,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="557" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="557" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A557" s="110" t="s">
         <v>814</v>
       </c>
@@ -13048,7 +13048,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="558" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="558" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A558" s="110" t="s">
         <v>815</v>
       </c>
@@ -13061,7 +13061,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="559" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="559" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A559" s="110" t="s">
         <v>816</v>
       </c>
@@ -13074,7 +13074,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="560" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="560" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A560" s="110" t="s">
         <v>817</v>
       </c>
@@ -13087,7 +13087,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="561" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="561" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A561" s="110" t="s">
         <v>818</v>
       </c>
@@ -13100,7 +13100,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="562" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="562" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A562" s="110" t="s">
         <v>819</v>
       </c>
@@ -13113,7 +13113,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="563" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="563" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A563" s="110" t="s">
         <v>820</v>
       </c>
@@ -13126,7 +13126,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="564" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="564" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A564" s="110" t="s">
         <v>821</v>
       </c>
@@ -13139,7 +13139,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="565" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="565" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A565" s="110" t="s">
         <v>822</v>
       </c>
@@ -13152,7 +13152,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="566" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="566" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A566" s="110" t="s">
         <v>823</v>
       </c>
@@ -13165,7 +13165,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="567" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="567" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A567" s="110" t="s">
         <v>824</v>
       </c>
@@ -13178,7 +13178,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="568" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="568" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A568" s="110" t="s">
         <v>825</v>
       </c>
@@ -13191,7 +13191,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="569" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="569" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A569" s="110" t="s">
         <v>826</v>
       </c>
@@ -13204,7 +13204,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="570" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="570" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A570" s="110" t="s">
         <v>827</v>
       </c>
@@ -13217,7 +13217,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="571" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="571" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A571" s="110" t="s">
         <v>828</v>
       </c>
@@ -13230,7 +13230,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="572" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="572" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A572" s="110" t="s">
         <v>829</v>
       </c>
@@ -13243,7 +13243,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="573" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="573" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A573" s="108" t="s">
         <v>830</v>
       </c>
@@ -13256,7 +13256,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="574" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="574" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A574" s="107" t="s">
         <v>831</v>
       </c>
@@ -13269,7 +13269,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="575" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="575" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A575" s="107" t="s">
         <v>832</v>
       </c>
@@ -13282,7 +13282,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="576" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="576" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A576" s="107" t="s">
         <v>833</v>
       </c>
@@ -13295,7 +13295,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="577" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="577" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A577" s="107" t="s">
         <v>834</v>
       </c>
@@ -13308,7 +13308,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="578" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="578" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A578" s="107" t="s">
         <v>835</v>
       </c>
@@ -13321,7 +13321,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="579" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="579" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A579" s="107" t="s">
         <v>836</v>
       </c>
@@ -13334,7 +13334,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="580" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="580" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A580" s="107" t="s">
         <v>837</v>
       </c>
@@ -13347,7 +13347,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="581" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="581" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A581" s="107" t="s">
         <v>838</v>
       </c>
@@ -13360,7 +13360,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="582" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="582" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A582" s="107" t="s">
         <v>839</v>
       </c>
@@ -13373,7 +13373,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="583" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="583" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A583" s="107" t="s">
         <v>840</v>
       </c>
@@ -13386,7 +13386,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="584" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="584" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A584" s="107" t="s">
         <v>841</v>
       </c>
@@ -13399,7 +13399,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="585" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="585" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A585" s="107" t="s">
         <v>842</v>
       </c>
@@ -13412,7 +13412,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="586" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="586" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A586" s="107" t="s">
         <v>843</v>
       </c>
@@ -13425,7 +13425,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="587" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="587" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A587" s="107" t="s">
         <v>844</v>
       </c>
@@ -13438,7 +13438,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="588" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="588" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A588" s="109" t="s">
         <v>845</v>
       </c>
@@ -13451,7 +13451,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="589" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="589" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A589" s="107" t="s">
         <v>846</v>
       </c>
@@ -13466,7 +13466,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="590" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="590" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A590" s="108" t="s">
         <v>847</v>
       </c>
@@ -13479,7 +13479,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="591" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="591" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A591" s="108" t="s">
         <v>848</v>
       </c>
@@ -13492,7 +13492,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="592" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="592" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A592" s="108" t="s">
         <v>849</v>
       </c>
@@ -13505,7 +13505,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="593" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="593" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A593" s="112" t="s">
         <v>850</v>
       </c>
@@ -13518,7 +13518,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="594" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="594" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A594" s="109" t="s">
         <v>851</v>
       </c>
@@ -13531,7 +13531,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="595" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="595" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A595" s="109" t="s">
         <v>852</v>
       </c>
@@ -13544,7 +13544,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="596" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="596" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A596" s="109" t="s">
         <v>853</v>
       </c>
@@ -13557,7 +13557,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="597" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="597" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A597" s="109" t="s">
         <v>854</v>
       </c>
@@ -13570,7 +13570,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="598" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="598" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A598" s="109" t="s">
         <v>855</v>
       </c>
@@ -13583,7 +13583,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="599" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="599" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A599" s="109" t="s">
         <v>856</v>
       </c>
@@ -13596,7 +13596,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="600" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="600" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A600" s="108" t="s">
         <v>857</v>
       </c>
@@ -13609,7 +13609,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="601" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="601" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A601" s="114" t="s">
         <v>858</v>
       </c>
@@ -13622,7 +13622,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="602" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="602" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A602" s="114" t="s">
         <v>859</v>
       </c>
@@ -13635,7 +13635,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="603" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="603" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A603" s="114" t="s">
         <v>860</v>
       </c>
@@ -13648,7 +13648,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="604" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="604" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A604" s="114" t="s">
         <v>861</v>
       </c>
@@ -13661,7 +13661,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="605" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="605" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A605" s="114" t="s">
         <v>862</v>
       </c>
@@ -13674,7 +13674,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="606" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="606" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A606" s="114" t="s">
         <v>863</v>
       </c>
@@ -13687,7 +13687,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="607" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="607" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A607" s="111" t="s">
         <v>864</v>
       </c>
@@ -13700,7 +13700,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="608" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="608" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A608" s="111" t="s">
         <v>865</v>
       </c>
@@ -13713,7 +13713,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="609" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="609" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A609" s="111" t="s">
         <v>866</v>
       </c>
@@ -13726,7 +13726,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="610" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="610" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A610" s="111" t="s">
         <v>867</v>
       </c>
@@ -13739,7 +13739,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="611" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="611" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A611" s="111" t="s">
         <v>868</v>
       </c>
@@ -13752,7 +13752,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="612" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="612" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A612" s="111" t="s">
         <v>869</v>
       </c>
@@ -13765,7 +13765,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="613" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="613" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A613" s="111" t="s">
         <v>870</v>
       </c>
@@ -13778,7 +13778,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="614" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="614" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A614" s="111" t="s">
         <v>871</v>
       </c>
@@ -13791,7 +13791,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="615" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="615" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A615" s="111" t="s">
         <v>872</v>
       </c>
@@ -13804,7 +13804,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="616" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="616" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A616" s="110" t="s">
         <v>873</v>
       </c>
@@ -13817,7 +13817,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="617" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="617" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A617" s="110" t="s">
         <v>874</v>
       </c>
@@ -13830,7 +13830,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="618" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="618" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A618" s="110" t="s">
         <v>875</v>
       </c>
@@ -13843,7 +13843,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="619" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="619" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A619" s="110" t="s">
         <v>876</v>
       </c>
@@ -13856,7 +13856,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="620" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="620" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A620" s="110" t="s">
         <v>877</v>
       </c>
@@ -13869,7 +13869,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="621" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="621" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A621" s="110" t="s">
         <v>878</v>
       </c>
@@ -13882,7 +13882,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="622" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="622" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A622" s="110" t="s">
         <v>879</v>
       </c>
@@ -13895,7 +13895,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="623" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="623" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A623" s="110" t="s">
         <v>880</v>
       </c>
@@ -13908,7 +13908,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="624" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="624" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A624" s="110" t="s">
         <v>881</v>
       </c>
@@ -13921,7 +13921,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="625" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="625" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A625" s="110" t="s">
         <v>882</v>
       </c>
@@ -13934,7 +13934,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="626" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="626" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A626" s="110" t="s">
         <v>883</v>
       </c>
@@ -13947,7 +13947,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="627" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="627" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A627" s="110" t="s">
         <v>884</v>
       </c>
@@ -13960,7 +13960,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="628" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="628" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A628" s="110" t="s">
         <v>885</v>
       </c>
@@ -13973,7 +13973,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="629" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="629" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A629" s="110" t="s">
         <v>886</v>
       </c>
@@ -13986,7 +13986,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="630" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="630" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A630" s="110" t="s">
         <v>887</v>
       </c>
@@ -13999,7 +13999,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="631" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="631" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A631" s="110" t="s">
         <v>888</v>
       </c>
@@ -14012,7 +14012,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="632" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="632" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A632" s="110" t="s">
         <v>889</v>
       </c>
@@ -14025,7 +14025,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="633" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="633" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A633" s="110" t="s">
         <v>890</v>
       </c>
@@ -14038,7 +14038,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="634" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="634" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A634" s="111" t="s">
         <v>891</v>
       </c>
@@ -14051,7 +14051,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="635" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="635" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A635" s="111" t="s">
         <v>892</v>
       </c>
@@ -14064,7 +14064,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="636" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="636" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A636" s="111" t="s">
         <v>893</v>
       </c>
@@ -14077,7 +14077,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="637" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="637" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A637" s="111" t="s">
         <v>894</v>
       </c>
@@ -14090,7 +14090,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="638" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="638" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A638" s="111" t="s">
         <v>895</v>
       </c>
@@ -14103,7 +14103,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="639" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="639" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A639" s="111" t="s">
         <v>896</v>
       </c>
@@ -14116,7 +14116,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="640" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="640" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A640" s="111" t="s">
         <v>897</v>
       </c>
@@ -14129,7 +14129,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="641" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="641" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A641" s="111" t="s">
         <v>898</v>
       </c>
@@ -14142,7 +14142,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="642" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="642" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A642" s="111" t="s">
         <v>899</v>
       </c>
@@ -14155,7 +14155,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="643" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="643" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A643" s="111" t="s">
         <v>900</v>
       </c>
@@ -14168,7 +14168,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="644" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="644" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A644" s="111" t="s">
         <v>901</v>
       </c>
@@ -14181,7 +14181,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="645" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="645" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A645" s="110" t="s">
         <v>902</v>
       </c>
@@ -14194,7 +14194,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="646" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="646" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A646" s="110" t="s">
         <v>903</v>
       </c>
@@ -14207,7 +14207,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="647" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="647" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A647" s="110" t="s">
         <v>904</v>
       </c>
@@ -14220,7 +14220,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="648" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="648" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A648" s="110" t="s">
         <v>905</v>
       </c>
@@ -14233,7 +14233,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="649" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="649" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A649" s="110" t="s">
         <v>906</v>
       </c>
@@ -14246,7 +14246,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="650" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="650" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A650" s="110" t="s">
         <v>907</v>
       </c>
@@ -14259,7 +14259,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="651" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="651" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A651" s="110" t="s">
         <v>908</v>
       </c>
@@ -14272,7 +14272,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="652" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="652" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A652" s="110" t="s">
         <v>909</v>
       </c>
@@ -14285,7 +14285,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="653" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="653" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A653" s="110" t="s">
         <v>910</v>
       </c>
@@ -14298,7 +14298,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="654" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="654" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A654" s="110" t="s">
         <v>911</v>
       </c>
@@ -14311,7 +14311,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="655" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="655" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A655" s="110" t="s">
         <v>912</v>
       </c>
@@ -14324,7 +14324,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="656" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="656" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A656" s="110" t="s">
         <v>913</v>
       </c>
@@ -14337,7 +14337,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="657" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="657" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A657" s="110" t="s">
         <v>914</v>
       </c>
@@ -14350,7 +14350,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="658" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="658" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A658" s="110" t="s">
         <v>915</v>
       </c>
@@ -14363,7 +14363,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="659" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="659" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A659" s="110" t="s">
         <v>916</v>
       </c>
@@ -14376,7 +14376,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="660" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="660" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A660" s="110" t="s">
         <v>917</v>
       </c>
@@ -14389,7 +14389,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="661" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="661" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A661" s="110" t="s">
         <v>918</v>
       </c>
@@ -14402,7 +14402,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="662" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="662" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A662" s="110" t="s">
         <v>919</v>
       </c>
@@ -14415,7 +14415,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="663" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="663" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A663" s="110" t="s">
         <v>920</v>
       </c>
@@ -14428,7 +14428,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="664" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="664" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A664" s="110" t="s">
         <v>921</v>
       </c>
@@ -14441,7 +14441,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="665" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="665" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A665" s="110" t="s">
         <v>922</v>
       </c>
@@ -14454,7 +14454,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="666" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="666" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A666" s="110" t="s">
         <v>923</v>
       </c>
@@ -14467,7 +14467,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="667" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="667" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A667" s="110" t="s">
         <v>924</v>
       </c>
@@ -14480,7 +14480,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="668" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="668" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A668" s="110" t="s">
         <v>925</v>
       </c>
@@ -14493,7 +14493,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="669" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="669" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A669" s="110" t="s">
         <v>926</v>
       </c>
@@ -14506,7 +14506,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="670" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="670" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A670" s="110" t="s">
         <v>927</v>
       </c>
@@ -14519,7 +14519,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="671" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="671" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A671" s="110" t="s">
         <v>928</v>
       </c>
@@ -14532,7 +14532,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="672" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="672" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A672" s="110" t="s">
         <v>929</v>
       </c>
@@ -14545,7 +14545,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="673" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="673" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A673" s="110" t="s">
         <v>930</v>
       </c>
@@ -14558,7 +14558,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="674" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="674" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A674" s="110" t="s">
         <v>931</v>
       </c>
@@ -14571,7 +14571,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="675" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="675" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A675" s="110" t="s">
         <v>932</v>
       </c>
@@ -14584,7 +14584,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="676" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="676" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A676" s="110" t="s">
         <v>933</v>
       </c>
@@ -14597,7 +14597,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="677" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="677" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A677" s="110" t="s">
         <v>934</v>
       </c>
@@ -14610,7 +14610,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="678" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="678" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A678" s="110" t="s">
         <v>935</v>
       </c>
@@ -14623,7 +14623,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="679" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="679" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A679" s="110" t="s">
         <v>936</v>
       </c>
@@ -14636,7 +14636,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="680" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="680" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A680" s="110" t="s">
         <v>937</v>
       </c>
@@ -14649,7 +14649,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="681" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="681" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A681" s="110" t="s">
         <v>938</v>
       </c>
@@ -14662,7 +14662,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="682" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="682" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A682" s="110" t="s">
         <v>939</v>
       </c>
@@ -14675,7 +14675,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="683" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="683" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A683" s="110" t="s">
         <v>940</v>
       </c>
@@ -14688,7 +14688,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="684" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="684" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A684" s="110" t="s">
         <v>941</v>
       </c>
@@ -14701,7 +14701,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="685" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="685" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A685" s="110" t="s">
         <v>942</v>
       </c>
@@ -14714,7 +14714,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="686" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="686" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A686" s="110" t="s">
         <v>943</v>
       </c>
@@ -14727,7 +14727,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="687" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="687" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A687" s="110" t="s">
         <v>944</v>
       </c>
@@ -14740,7 +14740,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="688" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="688" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A688" s="110" t="s">
         <v>945</v>
       </c>
@@ -14753,7 +14753,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="689" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="689" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A689" s="110" t="s">
         <v>946</v>
       </c>
@@ -14766,7 +14766,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="690" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="690" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A690" s="112" t="s">
         <v>947</v>
       </c>
@@ -14779,7 +14779,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="691" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="691" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A691" s="107" t="s">
         <v>948</v>
       </c>
@@ -15073,7 +15073,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E711" xr:uid="{00000000-0009-0000-0000-000009000000}"/>
+  <autoFilter ref="A1:E711" xr:uid="{00000000-0009-0000-0000-000009000000}">
+    <filterColumn colId="4">
+      <filters>
+        <filter val="ELECTRICITY"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -33343,19 +33349,19 @@
       <c r="B1" s="23" t="s">
         <v>1167</v>
       </c>
-      <c r="C1" s="198" t="s">
+      <c r="C1" s="204" t="s">
         <v>63</v>
       </c>
-      <c r="D1" s="177"/>
+      <c r="D1" s="183"/>
       <c r="E1" s="26" t="s">
         <v>1168</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A2" s="201" t="s">
+      <c r="A2" s="192" t="s">
         <v>76</v>
       </c>
-      <c r="B2" s="184"/>
+      <c r="B2" s="177"/>
       <c r="C2" s="129" t="s">
         <v>1043</v>
       </c>
@@ -33367,8 +33373,8 @@
       </c>
     </row>
     <row r="3" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="185"/>
-      <c r="B3" s="186"/>
+      <c r="A3" s="178"/>
+      <c r="B3" s="179"/>
       <c r="C3" s="130" t="s">
         <v>977</v>
       </c>
@@ -33380,8 +33386,8 @@
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A4" s="185"/>
-      <c r="B4" s="186"/>
+      <c r="A4" s="178"/>
+      <c r="B4" s="179"/>
       <c r="C4" s="129" t="s">
         <v>1172</v>
       </c>
@@ -33393,8 +33399,8 @@
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A5" s="185"/>
-      <c r="B5" s="186"/>
+      <c r="A5" s="178"/>
+      <c r="B5" s="179"/>
       <c r="C5" s="129" t="s">
         <v>1174</v>
       </c>
@@ -33406,8 +33412,8 @@
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A6" s="185"/>
-      <c r="B6" s="186"/>
+      <c r="A6" s="178"/>
+      <c r="B6" s="179"/>
       <c r="C6" s="129" t="s">
         <v>1061</v>
       </c>
@@ -33419,8 +33425,8 @@
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A7" s="185"/>
-      <c r="B7" s="186"/>
+      <c r="A7" s="178"/>
+      <c r="B7" s="179"/>
       <c r="C7" s="129" t="s">
         <v>1038</v>
       </c>
@@ -33432,8 +33438,8 @@
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A8" s="185"/>
-      <c r="B8" s="186"/>
+      <c r="A8" s="178"/>
+      <c r="B8" s="179"/>
       <c r="C8" s="131" t="s">
         <v>1101</v>
       </c>
@@ -33445,8 +33451,8 @@
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A9" s="185"/>
-      <c r="B9" s="186"/>
+      <c r="A9" s="178"/>
+      <c r="B9" s="179"/>
       <c r="C9" s="49" t="s">
         <v>1054</v>
       </c>
@@ -33458,8 +33464,8 @@
       </c>
     </row>
     <row r="10" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="185"/>
-      <c r="B10" s="186"/>
+      <c r="A10" s="178"/>
+      <c r="B10" s="179"/>
       <c r="C10" s="129" t="s">
         <v>1117</v>
       </c>
@@ -33471,8 +33477,8 @@
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A11" s="185"/>
-      <c r="B11" s="186"/>
+      <c r="A11" s="178"/>
+      <c r="B11" s="179"/>
       <c r="C11" s="129" t="s">
         <v>1067</v>
       </c>
@@ -33484,8 +33490,8 @@
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A12" s="185"/>
-      <c r="B12" s="186"/>
+      <c r="A12" s="178"/>
+      <c r="B12" s="179"/>
       <c r="C12" s="129" t="s">
         <v>991</v>
       </c>
@@ -33497,8 +33503,8 @@
       </c>
     </row>
     <row r="13" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="185"/>
-      <c r="B13" s="186"/>
+      <c r="A13" s="178"/>
+      <c r="B13" s="179"/>
       <c r="C13" s="129" t="s">
         <v>1064</v>
       </c>
@@ -33510,8 +33516,8 @@
       </c>
     </row>
     <row r="14" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="185"/>
-      <c r="B14" s="186"/>
+      <c r="A14" s="178"/>
+      <c r="B14" s="179"/>
       <c r="C14" s="132" t="s">
         <v>1097</v>
       </c>
@@ -33523,8 +33529,8 @@
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A15" s="185"/>
-      <c r="B15" s="186"/>
+      <c r="A15" s="178"/>
+      <c r="B15" s="179"/>
       <c r="C15" s="129" t="s">
         <v>1006</v>
       </c>
@@ -33536,8 +33542,8 @@
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A16" s="185"/>
-      <c r="B16" s="186"/>
+      <c r="A16" s="178"/>
+      <c r="B16" s="179"/>
       <c r="C16" s="129" t="s">
         <v>1069</v>
       </c>
@@ -33549,8 +33555,8 @@
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A17" s="185"/>
-      <c r="B17" s="186"/>
+      <c r="A17" s="178"/>
+      <c r="B17" s="179"/>
       <c r="C17" s="129" t="s">
         <v>1137</v>
       </c>
@@ -33562,8 +33568,8 @@
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A18" s="185"/>
-      <c r="B18" s="186"/>
+      <c r="A18" s="178"/>
+      <c r="B18" s="179"/>
       <c r="C18" s="129" t="s">
         <v>1188</v>
       </c>
@@ -33575,8 +33581,8 @@
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A19" s="185"/>
-      <c r="B19" s="186"/>
+      <c r="A19" s="178"/>
+      <c r="B19" s="179"/>
       <c r="C19" s="129" t="s">
         <v>1190</v>
       </c>
@@ -33588,8 +33594,8 @@
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A20" s="185"/>
-      <c r="B20" s="186"/>
+      <c r="A20" s="178"/>
+      <c r="B20" s="179"/>
       <c r="C20" s="129" t="s">
         <v>1192</v>
       </c>
@@ -33601,8 +33607,8 @@
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A21" s="185"/>
-      <c r="B21" s="186"/>
+      <c r="A21" s="178"/>
+      <c r="B21" s="179"/>
       <c r="C21" s="129" t="s">
         <v>1066</v>
       </c>
@@ -33614,8 +33620,8 @@
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A22" s="185"/>
-      <c r="B22" s="186"/>
+      <c r="A22" s="178"/>
+      <c r="B22" s="179"/>
       <c r="C22" s="49" t="s">
         <v>1111</v>
       </c>
@@ -33627,8 +33633,8 @@
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A23" s="185"/>
-      <c r="B23" s="186"/>
+      <c r="A23" s="178"/>
+      <c r="B23" s="179"/>
       <c r="C23" s="131" t="s">
         <v>984</v>
       </c>
@@ -33640,8 +33646,8 @@
       </c>
     </row>
     <row r="24" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="185"/>
-      <c r="B24" s="186"/>
+      <c r="A24" s="178"/>
+      <c r="B24" s="179"/>
       <c r="C24" s="133" t="s">
         <v>986</v>
       </c>
@@ -33653,8 +33659,8 @@
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A25" s="185"/>
-      <c r="B25" s="186"/>
+      <c r="A25" s="178"/>
+      <c r="B25" s="179"/>
       <c r="C25" s="129" t="s">
         <v>1013</v>
       </c>
@@ -33666,8 +33672,8 @@
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A26" s="185"/>
-      <c r="B26" s="186"/>
+      <c r="A26" s="178"/>
+      <c r="B26" s="179"/>
       <c r="C26" s="4" t="s">
         <v>1058</v>
       </c>
@@ -33679,8 +33685,8 @@
       </c>
     </row>
     <row r="27" spans="1:5" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="202"/>
-      <c r="B27" s="203"/>
+      <c r="A27" s="193"/>
+      <c r="B27" s="194"/>
       <c r="C27" s="37" t="s">
         <v>1201</v>
       </c>
@@ -33692,10 +33698,10 @@
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A28" s="204" t="s">
+      <c r="A28" s="195" t="s">
         <v>78</v>
       </c>
-      <c r="B28" s="205" t="s">
+      <c r="B28" s="196" t="s">
         <v>78</v>
       </c>
       <c r="C28" s="74" t="s">
@@ -33707,8 +33713,8 @@
       <c r="E28" s="153"/>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A29" s="186"/>
-      <c r="B29" s="192"/>
+      <c r="A29" s="179"/>
+      <c r="B29" s="191"/>
       <c r="C29" s="21" t="s">
         <v>1204</v>
       </c>
@@ -33717,8 +33723,8 @@
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A30" s="186"/>
-      <c r="B30" s="190" t="s">
+      <c r="A30" s="179"/>
+      <c r="B30" s="199" t="s">
         <v>1206</v>
       </c>
       <c r="C30" s="21" t="s">
@@ -33732,8 +33738,8 @@
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A31" s="186"/>
-      <c r="B31" s="192"/>
+      <c r="A31" s="179"/>
+      <c r="B31" s="191"/>
       <c r="C31" s="21" t="s">
         <v>1204</v>
       </c>
@@ -33745,8 +33751,8 @@
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A32" s="186"/>
-      <c r="B32" s="190" t="s">
+      <c r="A32" s="179"/>
+      <c r="B32" s="199" t="s">
         <v>1209</v>
       </c>
       <c r="C32" s="52" t="s">
@@ -33760,8 +33766,8 @@
       </c>
     </row>
     <row r="33" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="186"/>
-      <c r="B33" s="191"/>
+      <c r="A33" s="179"/>
+      <c r="B33" s="198"/>
       <c r="C33" s="4" t="s">
         <v>1079</v>
       </c>
@@ -33771,8 +33777,8 @@
       <c r="E33" s="48"/>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A34" s="186"/>
-      <c r="B34" s="191"/>
+      <c r="A34" s="179"/>
+      <c r="B34" s="198"/>
       <c r="C34" s="52" t="s">
         <v>1018</v>
       </c>
@@ -33782,8 +33788,8 @@
       <c r="E34" s="48"/>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A35" s="186"/>
-      <c r="B35" s="192"/>
+      <c r="A35" s="179"/>
+      <c r="B35" s="191"/>
       <c r="C35" s="4" t="s">
         <v>1073</v>
       </c>
@@ -33795,8 +33801,8 @@
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A36" s="186"/>
-      <c r="B36" s="190" t="s">
+      <c r="A36" s="179"/>
+      <c r="B36" s="199" t="s">
         <v>1216</v>
       </c>
       <c r="C36" s="21" t="s">
@@ -33810,8 +33816,8 @@
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A37" s="186"/>
-      <c r="B37" s="191"/>
+      <c r="A37" s="179"/>
+      <c r="B37" s="198"/>
       <c r="C37" s="21" t="s">
         <v>1035</v>
       </c>
@@ -33823,8 +33829,8 @@
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A38" s="186"/>
-      <c r="B38" s="191"/>
+      <c r="A38" s="179"/>
+      <c r="B38" s="198"/>
       <c r="C38" s="21" t="s">
         <v>1109</v>
       </c>
@@ -33836,8 +33842,8 @@
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A39" s="186"/>
-      <c r="B39" s="192"/>
+      <c r="A39" s="179"/>
+      <c r="B39" s="191"/>
       <c r="C39" s="4" t="s">
         <v>1073</v>
       </c>
@@ -33847,8 +33853,8 @@
       <c r="E39" s="48"/>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A40" s="186"/>
-      <c r="B40" s="195" t="s">
+      <c r="A40" s="179"/>
+      <c r="B40" s="201" t="s">
         <v>1222</v>
       </c>
       <c r="C40" s="21" t="s">
@@ -33862,8 +33868,8 @@
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A41" s="186"/>
-      <c r="B41" s="191"/>
+      <c r="A41" s="179"/>
+      <c r="B41" s="198"/>
       <c r="C41" s="21" t="s">
         <v>1224</v>
       </c>
@@ -33875,8 +33881,8 @@
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A42" s="186"/>
-      <c r="B42" s="191"/>
+      <c r="A42" s="179"/>
+      <c r="B42" s="198"/>
       <c r="C42" s="21" t="s">
         <v>1226</v>
       </c>
@@ -33888,8 +33894,8 @@
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A43" s="186"/>
-      <c r="B43" s="191"/>
+      <c r="A43" s="179"/>
+      <c r="B43" s="198"/>
       <c r="C43" s="21" t="s">
         <v>182</v>
       </c>
@@ -33901,8 +33907,8 @@
       </c>
     </row>
     <row r="44" spans="1:5" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="203"/>
-      <c r="B44" s="196"/>
+      <c r="A44" s="194"/>
+      <c r="B44" s="202"/>
       <c r="C44" s="163" t="s">
         <v>1229</v>
       </c>
@@ -33914,10 +33920,10 @@
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A45" s="199" t="s">
+      <c r="A45" s="205" t="s">
         <v>84</v>
       </c>
-      <c r="B45" s="194"/>
+      <c r="B45" s="200"/>
       <c r="C45" s="152" t="s">
         <v>1145</v>
       </c>
@@ -33927,8 +33933,8 @@
       <c r="E45" s="166"/>
     </row>
     <row r="46" spans="1:5" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="185"/>
-      <c r="B46" s="186"/>
+      <c r="A46" s="178"/>
+      <c r="B46" s="179"/>
       <c r="C46" s="167" t="s">
         <v>1150</v>
       </c>
@@ -33937,10 +33943,10 @@
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A47" s="193" t="s">
+      <c r="A47" s="197" t="s">
         <v>1233</v>
       </c>
-      <c r="B47" s="194"/>
+      <c r="B47" s="200"/>
       <c r="C47" s="49" t="s">
         <v>1234</v>
       </c>
@@ -33950,8 +33956,8 @@
       <c r="E47" s="153"/>
     </row>
     <row r="48" spans="1:5" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="187"/>
-      <c r="B48" s="188"/>
+      <c r="A48" s="180"/>
+      <c r="B48" s="181"/>
       <c r="C48" s="37" t="s">
         <v>1235</v>
       </c>
@@ -33960,7 +33966,7 @@
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A49" s="193" t="s">
+      <c r="A49" s="197" t="s">
         <v>89</v>
       </c>
       <c r="B49" s="169" t="s">
@@ -33977,7 +33983,7 @@
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A50" s="191"/>
+      <c r="A50" s="198"/>
       <c r="B50" s="50" t="s">
         <v>1239</v>
       </c>
@@ -33992,8 +33998,8 @@
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A51" s="191"/>
-      <c r="B51" s="197" t="s">
+      <c r="A51" s="198"/>
+      <c r="B51" s="203" t="s">
         <v>1242</v>
       </c>
       <c r="C51" s="21" t="s">
@@ -34002,20 +34008,20 @@
       <c r="D51" s="75" t="s">
         <v>1244</v>
       </c>
-      <c r="E51" s="200" t="s">
+      <c r="E51" s="190" t="s">
         <v>1245</v>
       </c>
     </row>
     <row r="52" spans="1:5" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="192"/>
-      <c r="B52" s="192"/>
+      <c r="A52" s="191"/>
+      <c r="B52" s="191"/>
       <c r="C52" s="163" t="s">
         <v>1246</v>
       </c>
       <c r="D52" s="173" t="s">
         <v>1247</v>
       </c>
-      <c r="E52" s="192"/>
+      <c r="E52" s="191"/>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A53" s="170"/>
@@ -34043,6 +34049,8 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="A45:B46"/>
     <mergeCell ref="E51:E52"/>
     <mergeCell ref="A2:B27"/>
     <mergeCell ref="A28:A44"/>
@@ -34054,8 +34062,6 @@
     <mergeCell ref="A47:B48"/>
     <mergeCell ref="B40:B44"/>
     <mergeCell ref="B51:B52"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="A45:B46"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="D28" r:id="rId1" display="https://doi.org/10.1016/j.resconrec.2019.05.015" xr:uid="{00000000-0004-0000-0C00-000000000000}"/>

--- a/projects/critical_materials/excel_files/Material_intensities.xlsx
+++ b/projects/critical_materials/excel_files/Material_intensities.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10920"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10927"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Paolo/Documents/PdM_code/EnergyScope-Quebec/projects/critical_materials/excel_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D82F4D53-204B-A849-B17D-FF5B199CA5F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7581429C-EFEB-FB41-9E0B-BD870AB49239}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="36020" windowHeight="20960" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15980" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Table of content" sheetId="1" r:id="rId1"/>
@@ -4853,6 +4853,13 @@
     <xf numFmtId="0" fontId="16" fillId="38" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="39" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -4875,18 +4882,11 @@
     <xf numFmtId="0" fontId="0" fillId="39" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="39" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="16" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="39" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -23539,7 +23539,7 @@
       </c>
       <c r="G388" s="4"/>
     </row>
-    <row r="389" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="389" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A389" s="4" t="s">
         <v>1015</v>
       </c>
@@ -23562,7 +23562,7 @@
         <v>1019</v>
       </c>
     </row>
-    <row r="390" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="390" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A390" s="4" t="s">
         <v>1015</v>
       </c>
@@ -23585,7 +23585,7 @@
         <v>1072</v>
       </c>
     </row>
-    <row r="391" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="391" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A391" s="4" t="s">
         <v>1015</v>
       </c>
@@ -23606,7 +23606,7 @@
       </c>
       <c r="G391" s="4"/>
     </row>
-    <row r="392" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="392" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A392" s="4" t="s">
         <v>1015</v>
       </c>
@@ -23627,7 +23627,7 @@
       </c>
       <c r="G392" s="4"/>
     </row>
-    <row r="393" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="393" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A393" s="4" t="s">
         <v>1015</v>
       </c>
@@ -23650,7 +23650,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="394" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="394" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A394" s="4" t="s">
         <v>1015</v>
       </c>
@@ -23671,7 +23671,7 @@
       </c>
       <c r="G394" s="4"/>
     </row>
-    <row r="395" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="395" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A395" s="4" t="s">
         <v>1015</v>
       </c>
@@ -23694,7 +23694,7 @@
         <v>1077</v>
       </c>
     </row>
-    <row r="396" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="396" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A396" s="4" t="s">
         <v>1015</v>
       </c>
@@ -23715,7 +23715,7 @@
       </c>
       <c r="G396" s="4"/>
     </row>
-    <row r="397" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="397" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A397" s="4" t="s">
         <v>1015</v>
       </c>
@@ -23738,7 +23738,7 @@
         <v>1021</v>
       </c>
     </row>
-    <row r="398" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="398" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A398" s="4" t="s">
         <v>1015</v>
       </c>
@@ -23761,7 +23761,7 @@
         <v>1104</v>
       </c>
     </row>
-    <row r="399" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="399" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A399" s="4" t="s">
         <v>1015</v>
       </c>
@@ -23784,7 +23784,7 @@
         <v>1078</v>
       </c>
     </row>
-    <row r="400" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="400" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A400" s="4" t="s">
         <v>1015</v>
       </c>
@@ -23805,7 +23805,7 @@
       </c>
       <c r="G400" s="4"/>
     </row>
-    <row r="401" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="401" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A401" s="4" t="s">
         <v>1015</v>
       </c>
@@ -23826,7 +23826,7 @@
       </c>
       <c r="G401" s="4"/>
     </row>
-    <row r="402" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="402" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A402" s="4" t="s">
         <v>1015</v>
       </c>
@@ -23849,7 +23849,7 @@
         <v>1081</v>
       </c>
     </row>
-    <row r="403" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="403" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A403" s="4" t="s">
         <v>1015</v>
       </c>
@@ -23872,7 +23872,7 @@
         <v>1083</v>
       </c>
     </row>
-    <row r="404" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="404" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A404" s="4" t="s">
         <v>1015</v>
       </c>
@@ -23893,7 +23893,7 @@
       </c>
       <c r="G404" s="4"/>
     </row>
-    <row r="405" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="405" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A405" s="4" t="s">
         <v>1015</v>
       </c>
@@ -23916,7 +23916,7 @@
         <v>1085</v>
       </c>
     </row>
-    <row r="406" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="406" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A406" s="4" t="s">
         <v>1015</v>
       </c>
@@ -23939,7 +23939,7 @@
         <v>1024</v>
       </c>
     </row>
-    <row r="407" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="407" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A407" s="4" t="s">
         <v>1015</v>
       </c>
@@ -23962,7 +23962,7 @@
         <v>1086</v>
       </c>
     </row>
-    <row r="408" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="408" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A408" s="4" t="s">
         <v>1015</v>
       </c>
@@ -23983,7 +23983,7 @@
       </c>
       <c r="G408" s="4"/>
     </row>
-    <row r="409" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="409" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A409" s="4" t="s">
         <v>1015</v>
       </c>
@@ -24006,7 +24006,7 @@
         <v>1089</v>
       </c>
     </row>
-    <row r="410" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="410" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A410" s="4" t="s">
         <v>1015</v>
       </c>
@@ -24029,7 +24029,7 @@
         <v>1090</v>
       </c>
     </row>
-    <row r="411" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="411" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A411" s="4" t="s">
         <v>1015</v>
       </c>
@@ -24050,7 +24050,7 @@
       </c>
       <c r="G411" s="4"/>
     </row>
-    <row r="412" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="412" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A412" s="4" t="s">
         <v>1015</v>
       </c>
@@ -24073,7 +24073,7 @@
         <v>1026</v>
       </c>
     </row>
-    <row r="413" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="413" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A413" s="4" t="s">
         <v>1015</v>
       </c>
@@ -24094,7 +24094,7 @@
       </c>
       <c r="G413" s="4"/>
     </row>
-    <row r="414" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="414" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A414" s="4" t="s">
         <v>1015</v>
       </c>
@@ -24117,7 +24117,7 @@
         <v>1092</v>
       </c>
     </row>
-    <row r="415" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="415" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A415" s="4" t="s">
         <v>1015</v>
       </c>
@@ -24140,7 +24140,7 @@
         <v>1028</v>
       </c>
     </row>
-    <row r="416" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="416" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A416" s="4" t="s">
         <v>1015</v>
       </c>
@@ -24163,7 +24163,7 @@
         <v>1030</v>
       </c>
     </row>
-    <row r="417" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="417" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A417" s="4" t="s">
         <v>1015</v>
       </c>
@@ -24186,7 +24186,7 @@
         <v>1093</v>
       </c>
     </row>
-    <row r="418" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="418" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A418" s="4" t="s">
         <v>1015</v>
       </c>
@@ -29455,7 +29455,7 @@
       </c>
       <c r="G660" s="4"/>
     </row>
-    <row r="661" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="661" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A661" s="4" t="s">
         <v>1003</v>
       </c>
@@ -29476,7 +29476,7 @@
       </c>
       <c r="G661" s="4"/>
     </row>
-    <row r="662" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="662" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A662" s="4" t="s">
         <v>1003</v>
       </c>
@@ -29499,7 +29499,7 @@
         <v>1065</v>
       </c>
     </row>
-    <row r="663" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="663" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A663" s="4" t="s">
         <v>1003</v>
       </c>
@@ -29520,7 +29520,7 @@
       </c>
       <c r="G663" s="4"/>
     </row>
-    <row r="664" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="664" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A664" s="4" t="s">
         <v>1003</v>
       </c>
@@ -29541,7 +29541,7 @@
       </c>
       <c r="G664" s="4"/>
     </row>
-    <row r="665" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="665" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A665" s="4" t="s">
         <v>1003</v>
       </c>
@@ -29562,7 +29562,7 @@
       </c>
       <c r="G665" s="4"/>
     </row>
-    <row r="666" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="666" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A666" s="4" t="s">
         <v>1003</v>
       </c>
@@ -31625,7 +31625,7 @@
       </c>
       <c r="G762" s="4"/>
     </row>
-    <row r="763" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="763" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A763" s="4" t="s">
         <v>1139</v>
       </c>
@@ -31646,7 +31646,7 @@
       </c>
       <c r="G763" s="4"/>
     </row>
-    <row r="764" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="764" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A764" s="4" t="s">
         <v>1139</v>
       </c>
@@ -31667,7 +31667,7 @@
       </c>
       <c r="G764" s="4"/>
     </row>
-    <row r="765" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="765" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A765" s="4" t="s">
         <v>1139</v>
       </c>
@@ -31688,7 +31688,7 @@
       </c>
       <c r="G765" s="4"/>
     </row>
-    <row r="766" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="766" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A766" s="4" t="s">
         <v>1139</v>
       </c>
@@ -33248,7 +33248,7 @@
   <autoFilter ref="A1:G837" xr:uid="{00000000-0009-0000-0000-00000A000000}">
     <filterColumn colId="2">
       <filters>
-        <filter val="Lithium"/>
+        <filter val="Tellurium"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -33349,7 +33349,7 @@
       <c r="B1" s="23" t="s">
         <v>1167</v>
       </c>
-      <c r="C1" s="204" t="s">
+      <c r="C1" s="190" t="s">
         <v>63</v>
       </c>
       <c r="D1" s="183"/>
@@ -33358,7 +33358,7 @@
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A2" s="192" t="s">
+      <c r="A2" s="195" t="s">
         <v>76</v>
       </c>
       <c r="B2" s="177"/>
@@ -33685,8 +33685,8 @@
       </c>
     </row>
     <row r="27" spans="1:5" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="193"/>
-      <c r="B27" s="194"/>
+      <c r="A27" s="196"/>
+      <c r="B27" s="197"/>
       <c r="C27" s="37" t="s">
         <v>1201</v>
       </c>
@@ -33698,10 +33698,10 @@
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A28" s="195" t="s">
+      <c r="A28" s="198" t="s">
         <v>78</v>
       </c>
-      <c r="B28" s="196" t="s">
+      <c r="B28" s="199" t="s">
         <v>78</v>
       </c>
       <c r="C28" s="74" t="s">
@@ -33714,7 +33714,7 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A29" s="179"/>
-      <c r="B29" s="191"/>
+      <c r="B29" s="194"/>
       <c r="C29" s="21" t="s">
         <v>1204</v>
       </c>
@@ -33724,7 +33724,7 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A30" s="179"/>
-      <c r="B30" s="199" t="s">
+      <c r="B30" s="202" t="s">
         <v>1206</v>
       </c>
       <c r="C30" s="21" t="s">
@@ -33739,7 +33739,7 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A31" s="179"/>
-      <c r="B31" s="191"/>
+      <c r="B31" s="194"/>
       <c r="C31" s="21" t="s">
         <v>1204</v>
       </c>
@@ -33752,7 +33752,7 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A32" s="179"/>
-      <c r="B32" s="199" t="s">
+      <c r="B32" s="202" t="s">
         <v>1209</v>
       </c>
       <c r="C32" s="52" t="s">
@@ -33767,7 +33767,7 @@
     </row>
     <row r="33" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="179"/>
-      <c r="B33" s="198"/>
+      <c r="B33" s="201"/>
       <c r="C33" s="4" t="s">
         <v>1079</v>
       </c>
@@ -33778,7 +33778,7 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A34" s="179"/>
-      <c r="B34" s="198"/>
+      <c r="B34" s="201"/>
       <c r="C34" s="52" t="s">
         <v>1018</v>
       </c>
@@ -33789,7 +33789,7 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A35" s="179"/>
-      <c r="B35" s="191"/>
+      <c r="B35" s="194"/>
       <c r="C35" s="4" t="s">
         <v>1073</v>
       </c>
@@ -33802,7 +33802,7 @@
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A36" s="179"/>
-      <c r="B36" s="199" t="s">
+      <c r="B36" s="202" t="s">
         <v>1216</v>
       </c>
       <c r="C36" s="21" t="s">
@@ -33817,7 +33817,7 @@
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A37" s="179"/>
-      <c r="B37" s="198"/>
+      <c r="B37" s="201"/>
       <c r="C37" s="21" t="s">
         <v>1035</v>
       </c>
@@ -33830,7 +33830,7 @@
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A38" s="179"/>
-      <c r="B38" s="198"/>
+      <c r="B38" s="201"/>
       <c r="C38" s="21" t="s">
         <v>1109</v>
       </c>
@@ -33843,7 +33843,7 @@
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A39" s="179"/>
-      <c r="B39" s="191"/>
+      <c r="B39" s="194"/>
       <c r="C39" s="4" t="s">
         <v>1073</v>
       </c>
@@ -33854,7 +33854,7 @@
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A40" s="179"/>
-      <c r="B40" s="201" t="s">
+      <c r="B40" s="203" t="s">
         <v>1222</v>
       </c>
       <c r="C40" s="21" t="s">
@@ -33869,7 +33869,7 @@
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A41" s="179"/>
-      <c r="B41" s="198"/>
+      <c r="B41" s="201"/>
       <c r="C41" s="21" t="s">
         <v>1224</v>
       </c>
@@ -33882,7 +33882,7 @@
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A42" s="179"/>
-      <c r="B42" s="198"/>
+      <c r="B42" s="201"/>
       <c r="C42" s="21" t="s">
         <v>1226</v>
       </c>
@@ -33895,7 +33895,7 @@
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A43" s="179"/>
-      <c r="B43" s="198"/>
+      <c r="B43" s="201"/>
       <c r="C43" s="21" t="s">
         <v>182</v>
       </c>
@@ -33907,8 +33907,8 @@
       </c>
     </row>
     <row r="44" spans="1:5" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="194"/>
-      <c r="B44" s="202"/>
+      <c r="A44" s="197"/>
+      <c r="B44" s="204"/>
       <c r="C44" s="163" t="s">
         <v>1229</v>
       </c>
@@ -33920,10 +33920,10 @@
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A45" s="205" t="s">
+      <c r="A45" s="191" t="s">
         <v>84</v>
       </c>
-      <c r="B45" s="200"/>
+      <c r="B45" s="192"/>
       <c r="C45" s="152" t="s">
         <v>1145</v>
       </c>
@@ -33943,10 +33943,10 @@
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A47" s="197" t="s">
+      <c r="A47" s="200" t="s">
         <v>1233</v>
       </c>
-      <c r="B47" s="200"/>
+      <c r="B47" s="192"/>
       <c r="C47" s="49" t="s">
         <v>1234</v>
       </c>
@@ -33966,7 +33966,7 @@
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A49" s="197" t="s">
+      <c r="A49" s="200" t="s">
         <v>89</v>
       </c>
       <c r="B49" s="169" t="s">
@@ -33983,7 +33983,7 @@
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A50" s="198"/>
+      <c r="A50" s="201"/>
       <c r="B50" s="50" t="s">
         <v>1239</v>
       </c>
@@ -33998,8 +33998,8 @@
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A51" s="198"/>
-      <c r="B51" s="203" t="s">
+      <c r="A51" s="201"/>
+      <c r="B51" s="205" t="s">
         <v>1242</v>
       </c>
       <c r="C51" s="21" t="s">
@@ -34008,20 +34008,20 @@
       <c r="D51" s="75" t="s">
         <v>1244</v>
       </c>
-      <c r="E51" s="190" t="s">
+      <c r="E51" s="193" t="s">
         <v>1245</v>
       </c>
     </row>
     <row r="52" spans="1:5" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="191"/>
-      <c r="B52" s="191"/>
+      <c r="A52" s="194"/>
+      <c r="B52" s="194"/>
       <c r="C52" s="163" t="s">
         <v>1246</v>
       </c>
       <c r="D52" s="173" t="s">
         <v>1247</v>
       </c>
-      <c r="E52" s="191"/>
+      <c r="E52" s="194"/>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A53" s="170"/>
@@ -38867,8 +38867,8 @@
       <c r="A5" s="40" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="120">
-        <v>0</v>
+      <c r="B5" s="122">
+        <v>11850</v>
       </c>
       <c r="C5" s="4">
         <v>560</v>
@@ -38880,7 +38880,7 @@
         <v>11850</v>
       </c>
       <c r="F5" s="4">
-        <v>0</v>
+        <v>11850</v>
       </c>
     </row>
     <row r="6" spans="1:29" x14ac:dyDescent="0.2">
@@ -39264,10 +39264,12 @@
         <v>74</v>
       </c>
       <c r="D25" s="122">
-        <v>1</v>
+        <f>D21/4</f>
+        <v>219</v>
       </c>
       <c r="E25" s="122">
-        <v>1</v>
+        <f>E21/4</f>
+        <v>242.25</v>
       </c>
       <c r="F25" s="118">
         <v>1</v>
@@ -39870,11 +39872,11 @@
       <c r="A5" s="40" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="24">
-        <v>0</v>
+      <c r="B5" s="4">
+        <v>11850</v>
       </c>
       <c r="C5" s="4">
-        <v>0</v>
+        <v>11850</v>
       </c>
       <c r="D5" s="24">
         <v>0</v>
@@ -40761,7 +40763,8 @@
         <v>0</v>
       </c>
       <c r="G25" s="4">
-        <v>1</v>
+        <f>G21/4</f>
+        <v>173.75</v>
       </c>
       <c r="H25" s="4">
         <v>0</v>
@@ -41318,13 +41321,13 @@
         <v>51</v>
       </c>
       <c r="B38" s="24">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C38" s="4">
         <v>20</v>
       </c>
       <c r="D38" s="24">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E38" s="4">
         <v>0</v>
@@ -41832,15 +41835,15 @@
       <c r="A5" s="40" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="151">
-        <v>0</v>
+      <c r="B5" s="4">
+        <v>118500</v>
       </c>
       <c r="C5" s="151">
         <v>0</v>
       </c>
       <c r="D5" s="4"/>
-      <c r="E5" s="151">
-        <v>0</v>
+      <c r="E5" s="4">
+        <v>118500</v>
       </c>
       <c r="F5" s="151">
         <v>0</v>
@@ -42764,8 +42767,8 @@
         <v>0</v>
       </c>
       <c r="H25" s="4">
-        <f>1/70</f>
-        <v>1.4285714285714285E-2</v>
+        <f>H21/4</f>
+        <v>2.4821428571428572</v>
       </c>
       <c r="I25" s="4">
         <v>0</v>

--- a/projects/critical_materials/excel_files/Material_intensities.xlsx
+++ b/projects/critical_materials/excel_files/Material_intensities.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10927"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11023"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Paolo/Documents/PdM_code/EnergyScope-Quebec/projects/critical_materials/excel_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7581429C-EFEB-FB41-9E0B-BD870AB49239}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C1D8AF3-06A6-744A-A154-4E146529564F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15980" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15980" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Table of content" sheetId="1" r:id="rId1"/>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7711" uniqueCount="1248">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7711" uniqueCount="1249">
   <si>
     <t>Metal_Intensity [g/vehicle]</t>
   </si>
@@ -3800,6 +3800,9 @@
   </si>
   <si>
     <t>Edelenbosch, O. Y., McCollum, D. L., Van Vuuren, D. P., Bertram, C., Carrara, S., Daly, H., Fujimori, S., Kitous, A., Kyle, P., Ó Broin, E., Karkatsoulis, P., et Sano, F. (2017). Decomposing passenger transport futures : Comparing results of global integrated assessment models. Transportation Research Part D: Transport and Environment, 55, 281‑293. https://doi.org/10.1016/j.trd.2016.07.003</t>
+  </si>
+  <si>
+    <t>Bieuville (copper taken from wataro)</t>
   </si>
 </sst>
 </file>
@@ -40005,7 +40008,7 @@
         <v>21</v>
       </c>
       <c r="B8" s="24">
-        <v>0</v>
+        <v>22300</v>
       </c>
       <c r="C8" s="4">
         <v>31500</v>
@@ -41497,7 +41500,7 @@
         <v>55</v>
       </c>
       <c r="B42" s="25" t="s">
-        <v>57</v>
+        <v>1248</v>
       </c>
       <c r="C42" s="25" t="s">
         <v>56</v>
